--- a/public/assets/exel/who.xlsx
+++ b/public/assets/exel/who.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="488">
   <si>
     <t>TUỔI</t>
   </si>
@@ -47,1204 +47,1450 @@
     <t>Tằn cân so với kỳ trước</t>
   </si>
   <si>
-    <t>49,1</t>
-  </si>
-  <si>
-    <t>3,2</t>
-  </si>
-  <si>
-    <t>53,7</t>
-  </si>
-  <si>
-    <t>4,2</t>
-  </si>
-  <si>
-    <t>4,6</t>
-  </si>
-  <si>
-    <t>1,0</t>
-  </si>
-  <si>
-    <t>56,1</t>
-  </si>
-  <si>
-    <t>4,8</t>
-  </si>
-  <si>
-    <t>2,4</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>58,5</t>
-  </si>
-  <si>
-    <t>5,4</t>
-  </si>
-  <si>
-    <t>60,9</t>
-  </si>
-  <si>
-    <t>6,1</t>
-  </si>
-  <si>
-    <t>63,3</t>
-  </si>
-  <si>
-    <t>6,7</t>
+    <t>49,90</t>
+  </si>
+  <si>
+    <t>3,30</t>
+  </si>
+  <si>
+    <t>54,70</t>
+  </si>
+  <si>
+    <t>4,50</t>
+  </si>
+  <si>
+    <t>4,80</t>
+  </si>
+  <si>
+    <t>1,20</t>
+  </si>
+  <si>
+    <t>56,85</t>
+  </si>
+  <si>
+    <t>5,18</t>
+  </si>
+  <si>
+    <t>2,15</t>
+  </si>
+  <si>
+    <t>0,68</t>
+  </si>
+  <si>
+    <t>59,00</t>
+  </si>
+  <si>
+    <t>5,86</t>
+  </si>
+  <si>
+    <t>61,15</t>
+  </si>
+  <si>
+    <t>6,54</t>
+  </si>
+  <si>
+    <t>63,30</t>
+  </si>
+  <si>
+    <t>7,22</t>
   </si>
   <si>
     <t>0,5</t>
   </si>
   <si>
-    <t>65,7</t>
-  </si>
-  <si>
-    <t>7,3</t>
-  </si>
-  <si>
-    <t>67,1</t>
-  </si>
-  <si>
-    <t>7,6</t>
-  </si>
-  <si>
-    <t>1,4</t>
-  </si>
-  <si>
-    <t>0,3</t>
-  </si>
-  <si>
-    <t>67,3</t>
-  </si>
-  <si>
-    <t>7,8</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>67,5</t>
-  </si>
-  <si>
-    <t>8,1</t>
-  </si>
-  <si>
-    <t>67,8</t>
-  </si>
-  <si>
-    <t>8,4</t>
-  </si>
-  <si>
-    <t>68,0</t>
-  </si>
-  <si>
-    <t>8,6</t>
-  </si>
-  <si>
-    <t>74,0</t>
-  </si>
-  <si>
-    <t>8,9</t>
-  </si>
-  <si>
-    <t>6,0</t>
-  </si>
-  <si>
-    <t>74,1</t>
-  </si>
-  <si>
-    <t>9,1</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>74,2</t>
-  </si>
-  <si>
-    <t>9,3</t>
-  </si>
-  <si>
-    <t>74,3</t>
-  </si>
-  <si>
-    <t>9,6</t>
-  </si>
-  <si>
-    <t>9,8</t>
-  </si>
-  <si>
-    <t>74,4</t>
-  </si>
-  <si>
-    <t>10,0</t>
-  </si>
-  <si>
-    <t>74,5</t>
-  </si>
-  <si>
-    <t>10,2</t>
-  </si>
-  <si>
-    <t>74,6</t>
-  </si>
-  <si>
-    <t>10,4</t>
-  </si>
-  <si>
-    <t>74,7</t>
-  </si>
-  <si>
-    <t>10,6</t>
-  </si>
-  <si>
-    <t>74,8</t>
-  </si>
-  <si>
-    <t>10,9</t>
-  </si>
-  <si>
-    <t>11,1</t>
-  </si>
-  <si>
-    <t>74,9</t>
-  </si>
-  <si>
-    <t>11,3</t>
-  </si>
-  <si>
-    <t>86,4</t>
-  </si>
-  <si>
-    <t>11,5</t>
-  </si>
-  <si>
-    <t>87,1</t>
-  </si>
-  <si>
-    <t>11,7</t>
-  </si>
-  <si>
-    <t>0,7</t>
-  </si>
-  <si>
-    <t>87,2</t>
-  </si>
-  <si>
-    <t>11,9</t>
-  </si>
-  <si>
-    <t>12,1</t>
-  </si>
-  <si>
-    <t>87,3</t>
-  </si>
-  <si>
-    <t>12,3</t>
-  </si>
-  <si>
-    <t>87,4</t>
-  </si>
-  <si>
-    <t>12,5</t>
-  </si>
-  <si>
-    <t>12,7</t>
-  </si>
-  <si>
-    <t>87,5</t>
-  </si>
-  <si>
-    <t>12,9</t>
-  </si>
-  <si>
-    <t>13,1</t>
-  </si>
-  <si>
-    <t>87,6</t>
-  </si>
-  <si>
-    <t>13,3</t>
-  </si>
-  <si>
-    <t>13,5</t>
-  </si>
-  <si>
-    <t>87,7</t>
-  </si>
-  <si>
-    <t>13,7</t>
-  </si>
-  <si>
-    <t>95,1</t>
-  </si>
-  <si>
-    <t>13,9</t>
-  </si>
-  <si>
-    <t>7,4</t>
-  </si>
-  <si>
-    <t>95,7</t>
-  </si>
-  <si>
-    <t>14,1</t>
-  </si>
-  <si>
-    <t>14,3</t>
-  </si>
-  <si>
-    <t>0,0</t>
-  </si>
-  <si>
-    <t>95,8</t>
-  </si>
-  <si>
-    <t>14,5</t>
-  </si>
-  <si>
-    <t>14,6</t>
-  </si>
-  <si>
-    <t>14,8</t>
-  </si>
-  <si>
-    <t>95,9</t>
-  </si>
-  <si>
-    <t>15,0</t>
-  </si>
-  <si>
-    <t>15,2</t>
-  </si>
-  <si>
-    <t>96,0</t>
-  </si>
-  <si>
-    <t>15,4</t>
-  </si>
-  <si>
-    <t>15,6</t>
-  </si>
-  <si>
-    <t>96,1</t>
-  </si>
-  <si>
-    <t>15,7</t>
-  </si>
-  <si>
-    <t>15,9</t>
-  </si>
-  <si>
-    <t>101,8</t>
-  </si>
-  <si>
-    <t>16,1</t>
-  </si>
-  <si>
-    <t>5,7</t>
-  </si>
-  <si>
-    <t>102,3</t>
-  </si>
-  <si>
-    <t>16,3</t>
-  </si>
-  <si>
-    <t>102,4</t>
-  </si>
-  <si>
-    <t>16,5</t>
-  </si>
-  <si>
-    <t>16,6</t>
-  </si>
-  <si>
-    <t>102,5</t>
-  </si>
-  <si>
-    <t>16,8</t>
-  </si>
-  <si>
-    <t>17,0</t>
-  </si>
-  <si>
-    <t>102,6</t>
-  </si>
-  <si>
-    <t>17,2</t>
-  </si>
-  <si>
-    <t>17,3</t>
-  </si>
-  <si>
-    <t>102,7</t>
-  </si>
-  <si>
-    <t>17,5</t>
-  </si>
-  <si>
-    <t>17,7</t>
-  </si>
-  <si>
-    <t>102,8</t>
-  </si>
-  <si>
-    <t>17,9</t>
-  </si>
-  <si>
-    <t>18,0</t>
-  </si>
-  <si>
-    <t>108,0</t>
-  </si>
-  <si>
-    <t>18,2</t>
-  </si>
-  <si>
-    <t>5,2</t>
-  </si>
-  <si>
-    <t>108,5</t>
-  </si>
-  <si>
-    <t>18,4</t>
-  </si>
-  <si>
-    <t>18,6</t>
-  </si>
-  <si>
-    <t>18,7</t>
-  </si>
-  <si>
-    <t>108,6</t>
-  </si>
-  <si>
-    <t>18,9</t>
-  </si>
-  <si>
-    <t>19,1</t>
-  </si>
-  <si>
-    <t>108,7</t>
-  </si>
-  <si>
-    <t>19,3</t>
-  </si>
-  <si>
-    <t>19,4</t>
-  </si>
-  <si>
-    <t>19,6</t>
-  </si>
-  <si>
-    <t>108,8</t>
-  </si>
-  <si>
-    <t>19,8</t>
-  </si>
-  <si>
-    <t>20,0</t>
-  </si>
-  <si>
-    <t>20,1</t>
-  </si>
-  <si>
-    <t>113,6</t>
-  </si>
-  <si>
-    <t>20,3</t>
-  </si>
-  <si>
-    <t>114,1</t>
-  </si>
-  <si>
-    <t>20,5</t>
-  </si>
-  <si>
-    <t>20,7</t>
-  </si>
-  <si>
-    <t>114,2</t>
-  </si>
-  <si>
-    <t>21,0</t>
-  </si>
-  <si>
-    <t>21,2</t>
-  </si>
-  <si>
-    <t>114,3</t>
-  </si>
-  <si>
-    <t>21,4</t>
-  </si>
-  <si>
-    <t>21,6</t>
-  </si>
-  <si>
-    <t>21,8</t>
-  </si>
-  <si>
-    <t>114,4</t>
-  </si>
-  <si>
-    <t>22,0</t>
-  </si>
-  <si>
-    <t>22,3</t>
-  </si>
-  <si>
-    <t>114,5</t>
-  </si>
-  <si>
-    <t>22,5</t>
-  </si>
-  <si>
-    <t>22,7</t>
-  </si>
-  <si>
-    <t>119,3</t>
-  </si>
-  <si>
-    <t>22,9</t>
-  </si>
-  <si>
-    <t>119,7</t>
-  </si>
-  <si>
-    <t>23,1</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>120,2</t>
-  </si>
-  <si>
-    <t>23,4</t>
-  </si>
-  <si>
-    <t>120,6</t>
-  </si>
-  <si>
-    <t>23,6</t>
-  </si>
-  <si>
-    <t>121,0</t>
-  </si>
-  <si>
-    <t>23,9</t>
-  </si>
-  <si>
-    <t>121,5</t>
-  </si>
-  <si>
-    <t>24,1</t>
-  </si>
-  <si>
-    <t>121,9</t>
-  </si>
-  <si>
-    <t>24,4</t>
-  </si>
-  <si>
-    <t>122,3</t>
-  </si>
-  <si>
-    <t>24,6</t>
-  </si>
-  <si>
-    <t>122,8</t>
-  </si>
-  <si>
-    <t>24,8</t>
-  </si>
-  <si>
-    <t>123,2</t>
-  </si>
-  <si>
-    <t>25,1</t>
-  </si>
-  <si>
-    <t>123,6</t>
-  </si>
-  <si>
-    <t>25,3</t>
-  </si>
-  <si>
-    <t>124,1</t>
-  </si>
-  <si>
-    <t>25,6</t>
-  </si>
-  <si>
-    <t>124,5</t>
-  </si>
-  <si>
-    <t>25,8</t>
-  </si>
-  <si>
-    <t>124,9</t>
-  </si>
-  <si>
-    <t>26,1</t>
-  </si>
-  <si>
-    <t>125,3</t>
-  </si>
-  <si>
-    <t>26,3</t>
-  </si>
-  <si>
-    <t>125,7</t>
-  </si>
-  <si>
-    <t>26,6</t>
-  </si>
-  <si>
-    <t>126,1</t>
-  </si>
-  <si>
-    <t>26,8</t>
-  </si>
-  <si>
-    <t>126,5</t>
-  </si>
-  <si>
-    <t>27,1</t>
-  </si>
-  <si>
-    <t>126,9</t>
-  </si>
-  <si>
-    <t>27,3</t>
-  </si>
-  <si>
-    <t>127,2</t>
-  </si>
-  <si>
-    <t>27,6</t>
-  </si>
-  <si>
-    <t>127,6</t>
-  </si>
-  <si>
-    <t>27,8</t>
-  </si>
-  <si>
-    <t>128,0</t>
-  </si>
-  <si>
-    <t>28,1</t>
-  </si>
-  <si>
-    <t>128,4</t>
-  </si>
-  <si>
-    <t>28,3</t>
-  </si>
-  <si>
-    <t>128,8</t>
-  </si>
-  <si>
-    <t>28,6</t>
-  </si>
-  <si>
-    <t>129,2</t>
-  </si>
-  <si>
-    <t>28,8</t>
-  </si>
-  <si>
-    <t>129,6</t>
-  </si>
-  <si>
-    <t>29,1</t>
-  </si>
-  <si>
-    <t>130,0</t>
-  </si>
-  <si>
-    <t>29,4</t>
-  </si>
-  <si>
-    <t>130,4</t>
-  </si>
-  <si>
-    <t>29,7</t>
-  </si>
-  <si>
-    <t>130,7</t>
-  </si>
-  <si>
-    <t>29,9</t>
-  </si>
-  <si>
-    <t>131,1</t>
-  </si>
-  <si>
-    <t>30,2</t>
-  </si>
-  <si>
-    <t>131,5</t>
-  </si>
-  <si>
-    <t>30,5</t>
-  </si>
-  <si>
-    <t>131,9</t>
-  </si>
-  <si>
-    <t>30,8</t>
-  </si>
-  <si>
-    <t>132,3</t>
-  </si>
-  <si>
-    <t>31,1</t>
-  </si>
-  <si>
-    <t>132,7</t>
-  </si>
-  <si>
-    <t>31,4</t>
-  </si>
-  <si>
-    <t>133,0</t>
-  </si>
-  <si>
-    <t>31,6</t>
-  </si>
-  <si>
-    <t>133,4</t>
-  </si>
-  <si>
-    <t>31,9</t>
-  </si>
-  <si>
-    <t>133,8</t>
-  </si>
-  <si>
-    <t>32,2</t>
-  </si>
-  <si>
-    <t>134,2</t>
-  </si>
-  <si>
-    <t>32,5</t>
-  </si>
-  <si>
-    <t>134,6</t>
-  </si>
-  <si>
-    <t>32,8</t>
-  </si>
-  <si>
-    <t>135,0</t>
-  </si>
-  <si>
-    <t>33,2</t>
-  </si>
-  <si>
-    <t>135,4</t>
-  </si>
-  <si>
-    <t>33,5</t>
-  </si>
-  <si>
-    <t>135,8</t>
-  </si>
-  <si>
-    <t>33,8</t>
-  </si>
-  <si>
-    <t>136,2</t>
-  </si>
-  <si>
-    <t>34,1</t>
-  </si>
-  <si>
-    <t>136,5</t>
-  </si>
-  <si>
-    <t>34,4</t>
-  </si>
-  <si>
-    <t>136,9</t>
-  </si>
-  <si>
-    <t>34,7</t>
-  </si>
-  <si>
-    <t>137,3</t>
-  </si>
-  <si>
-    <t>35,1</t>
-  </si>
-  <si>
-    <t>137,7</t>
-  </si>
-  <si>
-    <t>35,4</t>
-  </si>
-  <si>
-    <t>138,1</t>
-  </si>
-  <si>
-    <t>35,7</t>
-  </si>
-  <si>
-    <t>138,5</t>
-  </si>
-  <si>
-    <t>36,0</t>
-  </si>
-  <si>
-    <t>139,2</t>
-  </si>
-  <si>
-    <t>36,4</t>
-  </si>
-  <si>
-    <t>139,9</t>
-  </si>
-  <si>
-    <t>36,8</t>
-  </si>
-  <si>
-    <t>140,5</t>
-  </si>
-  <si>
-    <t>37,2</t>
-  </si>
-  <si>
-    <t>141,2</t>
-  </si>
-  <si>
-    <t>37,6</t>
-  </si>
-  <si>
-    <t>141,9</t>
-  </si>
-  <si>
-    <t>38,0</t>
-  </si>
-  <si>
-    <t>142,6</t>
-  </si>
-  <si>
-    <t>38,4</t>
-  </si>
-  <si>
-    <t>143,2</t>
-  </si>
-  <si>
-    <t>38,8</t>
-  </si>
-  <si>
-    <t>143,9</t>
-  </si>
-  <si>
-    <t>39,2</t>
-  </si>
-  <si>
-    <t>144,6</t>
-  </si>
-  <si>
-    <t>39,6</t>
-  </si>
-  <si>
-    <t>145,3</t>
-  </si>
-  <si>
-    <t>40,0</t>
-  </si>
-  <si>
-    <t>145,9</t>
-  </si>
-  <si>
-    <t>40,4</t>
-  </si>
-  <si>
-    <t>146,6</t>
-  </si>
-  <si>
-    <t>40,8</t>
-  </si>
-  <si>
-    <t>147,0</t>
-  </si>
-  <si>
-    <t>41,2</t>
-  </si>
-  <si>
-    <t>147,4</t>
-  </si>
-  <si>
-    <t>41,6</t>
-  </si>
-  <si>
-    <t>147,9</t>
-  </si>
-  <si>
-    <t>42,0</t>
-  </si>
-  <si>
-    <t>148,3</t>
-  </si>
-  <si>
-    <t>42,4</t>
-  </si>
-  <si>
-    <t>148,7</t>
-  </si>
-  <si>
-    <t>42,8</t>
-  </si>
-  <si>
-    <t>149,1</t>
-  </si>
-  <si>
-    <t>43,2</t>
-  </si>
-  <si>
-    <t>149,5</t>
-  </si>
-  <si>
-    <t>43,6</t>
-  </si>
-  <si>
-    <t>149,9</t>
-  </si>
-  <si>
-    <t>44,0</t>
-  </si>
-  <si>
-    <t>150,4</t>
-  </si>
-  <si>
-    <t>44,4</t>
-  </si>
-  <si>
-    <t>150,8</t>
-  </si>
-  <si>
-    <t>44,8</t>
-  </si>
-  <si>
-    <t>151,2</t>
-  </si>
-  <si>
-    <t>45,2</t>
-  </si>
-  <si>
-    <t>151,6</t>
-  </si>
-  <si>
-    <t>45,6</t>
-  </si>
-  <si>
-    <t>152,1</t>
-  </si>
-  <si>
-    <t>45,9</t>
-  </si>
-  <si>
-    <t>152,7</t>
-  </si>
-  <si>
-    <t>46,3</t>
-  </si>
-  <si>
-    <t>153,2</t>
-  </si>
-  <si>
-    <t>46,6</t>
-  </si>
-  <si>
-    <t>153,8</t>
-  </si>
-  <si>
-    <t>46,9</t>
-  </si>
-  <si>
-    <t>154,3</t>
-  </si>
-  <si>
-    <t>47,2</t>
-  </si>
-  <si>
-    <t>154,9</t>
-  </si>
-  <si>
-    <t>47,6</t>
-  </si>
-  <si>
-    <t>155,4</t>
-  </si>
-  <si>
-    <t>47,9</t>
-  </si>
-  <si>
-    <t>155,9</t>
-  </si>
-  <si>
-    <t>48,2</t>
-  </si>
-  <si>
-    <t>156,5</t>
-  </si>
-  <si>
-    <t>48,5</t>
-  </si>
-  <si>
-    <t>157,0</t>
-  </si>
-  <si>
-    <t>48,9</t>
-  </si>
-  <si>
-    <t>157,6</t>
-  </si>
-  <si>
-    <t>49,2</t>
-  </si>
-  <si>
-    <t>158,1</t>
-  </si>
-  <si>
-    <t>49,5</t>
-  </si>
-  <si>
-    <t>158,2</t>
-  </si>
-  <si>
-    <t>49,7</t>
-  </si>
-  <si>
-    <t>158,4</t>
-  </si>
-  <si>
-    <t>49,9</t>
-  </si>
-  <si>
-    <t>158,5</t>
-  </si>
-  <si>
-    <t>50,2</t>
-  </si>
-  <si>
-    <t>158,6</t>
-  </si>
-  <si>
-    <t>50,4</t>
-  </si>
-  <si>
-    <t>158,8</t>
-  </si>
-  <si>
-    <t>50,6</t>
-  </si>
-  <si>
-    <t>158,9</t>
-  </si>
-  <si>
-    <t>50,8</t>
-  </si>
-  <si>
-    <t>159,0</t>
-  </si>
-  <si>
-    <t>51,0</t>
-  </si>
-  <si>
-    <t>159,2</t>
-  </si>
-  <si>
-    <t>51,2</t>
-  </si>
-  <si>
-    <t>159,3</t>
-  </si>
-  <si>
-    <t>51,5</t>
-  </si>
-  <si>
-    <t>159,4</t>
-  </si>
-  <si>
-    <t>51,7</t>
-  </si>
-  <si>
-    <t>159,6</t>
-  </si>
-  <si>
-    <t>51,9</t>
-  </si>
-  <si>
-    <t>159,7</t>
-  </si>
-  <si>
-    <t>52,1</t>
-  </si>
-  <si>
-    <t>159,9</t>
-  </si>
-  <si>
-    <t>52,2</t>
-  </si>
-  <si>
-    <t>160,2</t>
-  </si>
-  <si>
-    <t>52,3</t>
-  </si>
-  <si>
-    <t>160,4</t>
-  </si>
-  <si>
-    <t>52,5</t>
-  </si>
-  <si>
-    <t>160,6</t>
-  </si>
-  <si>
-    <t>52,6</t>
-  </si>
-  <si>
-    <t>160,9</t>
-  </si>
-  <si>
-    <t>52,7</t>
-  </si>
-  <si>
-    <t>161,1</t>
-  </si>
-  <si>
-    <t>52,8</t>
-  </si>
-  <si>
-    <t>161,3</t>
-  </si>
-  <si>
-    <t>52,9</t>
-  </si>
-  <si>
-    <t>161,6</t>
-  </si>
-  <si>
-    <t>53,0</t>
-  </si>
-  <si>
-    <t>161,8</t>
-  </si>
-  <si>
-    <t>53,2</t>
-  </si>
-  <si>
-    <t>162,0</t>
-  </si>
-  <si>
-    <t>53,3</t>
-  </si>
-  <si>
-    <t>162,3</t>
-  </si>
-  <si>
-    <t>53,4</t>
-  </si>
-  <si>
-    <t>162,5</t>
-  </si>
-  <si>
-    <t>53,5</t>
-  </si>
-  <si>
-    <t>53,6</t>
-  </si>
-  <si>
-    <t>53,8</t>
-  </si>
-  <si>
-    <t>53,9</t>
-  </si>
-  <si>
-    <t>54,0</t>
-  </si>
-  <si>
-    <t>54,1</t>
-  </si>
-  <si>
-    <t>54,2</t>
-  </si>
-  <si>
-    <t>54,3</t>
-  </si>
-  <si>
-    <t>54,4</t>
-  </si>
-  <si>
-    <t>54,6</t>
-  </si>
-  <si>
-    <t>162,6</t>
-  </si>
-  <si>
-    <t>54,8</t>
-  </si>
-  <si>
-    <t>55,0</t>
-  </si>
-  <si>
-    <t>162,7</t>
-  </si>
-  <si>
-    <t>55,2</t>
-  </si>
-  <si>
-    <t>55,4</t>
-  </si>
-  <si>
-    <t>162,8</t>
-  </si>
-  <si>
-    <t>55,6</t>
-  </si>
-  <si>
-    <t>55,7</t>
-  </si>
-  <si>
-    <t>55,9</t>
-  </si>
-  <si>
-    <t>162,9</t>
-  </si>
-  <si>
-    <t>56,3</t>
-  </si>
-  <si>
-    <t>163,0</t>
-  </si>
-  <si>
-    <t>56,5</t>
-  </si>
-  <si>
-    <t>56,7</t>
-  </si>
-  <si>
-    <t>56,8</t>
-  </si>
-  <si>
-    <t>56,9</t>
-  </si>
-  <si>
-    <t>57,0</t>
-  </si>
-  <si>
-    <t>57,1</t>
+    <t>67,60</t>
+  </si>
+  <si>
+    <t>7,90</t>
+  </si>
+  <si>
+    <t>4,30</t>
+  </si>
+  <si>
+    <t>68,95</t>
+  </si>
+  <si>
+    <t>8,18</t>
+  </si>
+  <si>
+    <t>1,35</t>
+  </si>
+  <si>
+    <t>0,28</t>
+  </si>
+  <si>
+    <t>70,30</t>
+  </si>
+  <si>
+    <t>8,47</t>
+  </si>
+  <si>
+    <t>71,65</t>
+  </si>
+  <si>
+    <t>8,75</t>
+  </si>
+  <si>
+    <t>73,00</t>
+  </si>
+  <si>
+    <t>9,03</t>
+  </si>
+  <si>
+    <t>74,35</t>
+  </si>
+  <si>
+    <t>9,32</t>
+  </si>
+  <si>
+    <t>75,70</t>
+  </si>
+  <si>
+    <t>9,60</t>
+  </si>
+  <si>
+    <t>76,71</t>
+  </si>
+  <si>
+    <t>9,82</t>
+  </si>
+  <si>
+    <t>1,01</t>
+  </si>
+  <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>77,72</t>
+  </si>
+  <si>
+    <t>10,03</t>
+  </si>
+  <si>
+    <t>78,73</t>
+  </si>
+  <si>
+    <t>10,25</t>
+  </si>
+  <si>
+    <t>79,73</t>
+  </si>
+  <si>
+    <t>10,47</t>
+  </si>
+  <si>
+    <t>80,74</t>
+  </si>
+  <si>
+    <t>10,68</t>
+  </si>
+  <si>
+    <t>81,75</t>
+  </si>
+  <si>
+    <t>10,90</t>
+  </si>
+  <si>
+    <t>82,76</t>
+  </si>
+  <si>
+    <t>11,12</t>
+  </si>
+  <si>
+    <t>83,77</t>
+  </si>
+  <si>
+    <t>11,33</t>
+  </si>
+  <si>
+    <t>84,78</t>
+  </si>
+  <si>
+    <t>11,55</t>
+  </si>
+  <si>
+    <t>85,78</t>
+  </si>
+  <si>
+    <t>11,77</t>
+  </si>
+  <si>
+    <t>86,79</t>
+  </si>
+  <si>
+    <t>11,98</t>
+  </si>
+  <si>
+    <t>87,80</t>
+  </si>
+  <si>
+    <t>12,20</t>
+  </si>
+  <si>
+    <t>88,49</t>
+  </si>
+  <si>
+    <t>12,38</t>
+  </si>
+  <si>
+    <t>0,69</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>89,18</t>
+  </si>
+  <si>
+    <t>12,55</t>
+  </si>
+  <si>
+    <t>89,88</t>
+  </si>
+  <si>
+    <t>12,73</t>
+  </si>
+  <si>
+    <t>90,57</t>
+  </si>
+  <si>
+    <t>12,90</t>
+  </si>
+  <si>
+    <t>91,26</t>
+  </si>
+  <si>
+    <t>13,08</t>
+  </si>
+  <si>
+    <t>91,95</t>
+  </si>
+  <si>
+    <t>13,25</t>
+  </si>
+  <si>
+    <t>92,64</t>
+  </si>
+  <si>
+    <t>13,43</t>
+  </si>
+  <si>
+    <t>93,33</t>
+  </si>
+  <si>
+    <t>13,60</t>
+  </si>
+  <si>
+    <t>94,03</t>
+  </si>
+  <si>
+    <t>13,78</t>
+  </si>
+  <si>
+    <t>94,72</t>
+  </si>
+  <si>
+    <t>13,95</t>
+  </si>
+  <si>
+    <t>95,41</t>
+  </si>
+  <si>
+    <t>14,13</t>
+  </si>
+  <si>
+    <t>96,10</t>
+  </si>
+  <si>
+    <t>14,30</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>96,67</t>
+  </si>
+  <si>
+    <t>14,47</t>
+  </si>
+  <si>
+    <t>0,57</t>
+  </si>
+  <si>
+    <t>97,23</t>
+  </si>
+  <si>
+    <t>14,63</t>
+  </si>
+  <si>
+    <t>97,80</t>
+  </si>
+  <si>
+    <t>14,80</t>
+  </si>
+  <si>
+    <t>98,37</t>
+  </si>
+  <si>
+    <t>14,97</t>
+  </si>
+  <si>
+    <t>98,93</t>
+  </si>
+  <si>
+    <t>15,13</t>
+  </si>
+  <si>
+    <t>99,50</t>
+  </si>
+  <si>
+    <t>15,30</t>
+  </si>
+  <si>
+    <t>100,07</t>
+  </si>
+  <si>
+    <t>15,47</t>
+  </si>
+  <si>
+    <t>100,63</t>
+  </si>
+  <si>
+    <t>15,63</t>
+  </si>
+  <si>
+    <t>101,20</t>
+  </si>
+  <si>
+    <t>15,80</t>
+  </si>
+  <si>
+    <t>101,77</t>
+  </si>
+  <si>
+    <t>15,97</t>
+  </si>
+  <si>
+    <t>102,33</t>
+  </si>
+  <si>
+    <t>16,13</t>
+  </si>
+  <si>
+    <t>102,90</t>
+  </si>
+  <si>
+    <t>16,30</t>
+  </si>
+  <si>
+    <t>103,49</t>
+  </si>
+  <si>
+    <t>16,47</t>
+  </si>
+  <si>
+    <t>0,59</t>
+  </si>
+  <si>
+    <t>104,08</t>
+  </si>
+  <si>
+    <t>16,63</t>
+  </si>
+  <si>
+    <t>104,68</t>
+  </si>
+  <si>
+    <t>16,80</t>
+  </si>
+  <si>
+    <t>105,27</t>
+  </si>
+  <si>
+    <t>16,97</t>
+  </si>
+  <si>
+    <t>105,86</t>
+  </si>
+  <si>
+    <t>17,13</t>
+  </si>
+  <si>
+    <t>106,45</t>
+  </si>
+  <si>
+    <t>17,30</t>
+  </si>
+  <si>
+    <t>107,04</t>
+  </si>
+  <si>
+    <t>17,47</t>
+  </si>
+  <si>
+    <t>107,63</t>
+  </si>
+  <si>
+    <t>17,63</t>
+  </si>
+  <si>
+    <t>108,23</t>
+  </si>
+  <si>
+    <t>17,80</t>
+  </si>
+  <si>
+    <t>108,82</t>
+  </si>
+  <si>
+    <t>17,97</t>
+  </si>
+  <si>
+    <t>109,41</t>
+  </si>
+  <si>
+    <t>18,13</t>
+  </si>
+  <si>
+    <t>110,00</t>
+  </si>
+  <si>
+    <t>18,30</t>
+  </si>
+  <si>
+    <t>110,46</t>
+  </si>
+  <si>
+    <t>18,48</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>110,92</t>
+  </si>
+  <si>
+    <t>18,67</t>
+  </si>
+  <si>
+    <t>111,38</t>
+  </si>
+  <si>
+    <t>18,85</t>
+  </si>
+  <si>
+    <t>111,83</t>
+  </si>
+  <si>
+    <t>19,03</t>
+  </si>
+  <si>
+    <t>112,29</t>
+  </si>
+  <si>
+    <t>19,22</t>
+  </si>
+  <si>
+    <t>112,75</t>
+  </si>
+  <si>
+    <t>19,40</t>
+  </si>
+  <si>
+    <t>113,21</t>
+  </si>
+  <si>
+    <t>19,58</t>
+  </si>
+  <si>
+    <t>113,67</t>
+  </si>
+  <si>
+    <t>19,77</t>
+  </si>
+  <si>
+    <t>114,13</t>
+  </si>
+  <si>
+    <t>19,95</t>
+  </si>
+  <si>
+    <t>114,58</t>
+  </si>
+  <si>
+    <t>20,13</t>
+  </si>
+  <si>
+    <t>115,04</t>
+  </si>
+  <si>
+    <t>20,32</t>
+  </si>
+  <si>
+    <t>115,50</t>
+  </si>
+  <si>
+    <t>20,50</t>
+  </si>
+  <si>
+    <t>116,03</t>
+  </si>
+  <si>
+    <t>0,53</t>
+  </si>
+  <si>
+    <t>0,00</t>
+  </si>
+  <si>
+    <t>116,57</t>
+  </si>
+  <si>
+    <t>117,10</t>
+  </si>
+  <si>
+    <t>117,63</t>
+  </si>
+  <si>
+    <t>118,17</t>
+  </si>
+  <si>
+    <t>118,70</t>
+  </si>
+  <si>
+    <t>119,23</t>
+  </si>
+  <si>
+    <t>119,77</t>
+  </si>
+  <si>
+    <t>120,30</t>
+  </si>
+  <si>
+    <t>120,83</t>
+  </si>
+  <si>
+    <t>121,37</t>
+  </si>
+  <si>
+    <t>121,90</t>
+  </si>
+  <si>
+    <t>22,90</t>
+  </si>
+  <si>
+    <t>2,40</t>
+  </si>
+  <si>
+    <t>122,43</t>
+  </si>
+  <si>
+    <t>23,13</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>122,95</t>
+  </si>
+  <si>
+    <t>23,35</t>
+  </si>
+  <si>
+    <t>123,48</t>
+  </si>
+  <si>
+    <t>23,58</t>
+  </si>
+  <si>
+    <t>124,00</t>
+  </si>
+  <si>
+    <t>23,80</t>
+  </si>
+  <si>
+    <t>124,53</t>
+  </si>
+  <si>
+    <t>24,03</t>
+  </si>
+  <si>
+    <t>125,05</t>
+  </si>
+  <si>
+    <t>24,25</t>
+  </si>
+  <si>
+    <t>125,58</t>
+  </si>
+  <si>
+    <t>24,48</t>
+  </si>
+  <si>
+    <t>126,10</t>
+  </si>
+  <si>
+    <t>24,70</t>
+  </si>
+  <si>
+    <t>126,63</t>
+  </si>
+  <si>
+    <t>24,93</t>
+  </si>
+  <si>
+    <t>127,15</t>
+  </si>
+  <si>
+    <t>25,15</t>
+  </si>
+  <si>
+    <t>127,68</t>
+  </si>
+  <si>
+    <t>25,38</t>
+  </si>
+  <si>
+    <t>128,20</t>
+  </si>
+  <si>
+    <t>25,60</t>
+  </si>
+  <si>
+    <t>0,52</t>
+  </si>
+  <si>
+    <t>128,63</t>
+  </si>
+  <si>
+    <t>25,85</t>
+  </si>
+  <si>
+    <t>0,43</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>129,05</t>
+  </si>
+  <si>
+    <t>26,10</t>
+  </si>
+  <si>
+    <t>129,48</t>
+  </si>
+  <si>
+    <t>26,35</t>
+  </si>
+  <si>
+    <t>129,90</t>
+  </si>
+  <si>
+    <t>26,60</t>
+  </si>
+  <si>
+    <t>130,33</t>
+  </si>
+  <si>
+    <t>26,85</t>
+  </si>
+  <si>
+    <t>130,75</t>
+  </si>
+  <si>
+    <t>27,10</t>
+  </si>
+  <si>
+    <t>131,18</t>
+  </si>
+  <si>
+    <t>27,35</t>
+  </si>
+  <si>
+    <t>131,60</t>
+  </si>
+  <si>
+    <t>27,60</t>
+  </si>
+  <si>
+    <t>132,03</t>
+  </si>
+  <si>
+    <t>27,85</t>
+  </si>
+  <si>
+    <t>132,45</t>
+  </si>
+  <si>
+    <t>28,10</t>
+  </si>
+  <si>
+    <t>132,88</t>
+  </si>
+  <si>
+    <t>28,35</t>
+  </si>
+  <si>
+    <t>133,30</t>
+  </si>
+  <si>
+    <t>28,60</t>
+  </si>
+  <si>
+    <t>0,42</t>
+  </si>
+  <si>
+    <t>133,73</t>
+  </si>
+  <si>
+    <t>28,88</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>134,15</t>
+  </si>
+  <si>
+    <t>29,15</t>
+  </si>
+  <si>
+    <t>134,58</t>
+  </si>
+  <si>
+    <t>29,43</t>
+  </si>
+  <si>
+    <t>135,00</t>
+  </si>
+  <si>
+    <t>29,70</t>
+  </si>
+  <si>
+    <t>135,43</t>
+  </si>
+  <si>
+    <t>29,98</t>
+  </si>
+  <si>
+    <t>135,85</t>
+  </si>
+  <si>
+    <t>30,25</t>
+  </si>
+  <si>
+    <t>136,28</t>
+  </si>
+  <si>
+    <t>30,53</t>
+  </si>
+  <si>
+    <t>136,70</t>
+  </si>
+  <si>
+    <t>30,80</t>
+  </si>
+  <si>
+    <t>137,13</t>
+  </si>
+  <si>
+    <t>31,08</t>
+  </si>
+  <si>
+    <t>137,55</t>
+  </si>
+  <si>
+    <t>31,35</t>
+  </si>
+  <si>
+    <t>137,98</t>
+  </si>
+  <si>
+    <t>31,63</t>
+  </si>
+  <si>
+    <t>138,40</t>
+  </si>
+  <si>
+    <t>31,90</t>
+  </si>
+  <si>
+    <t>138,83</t>
+  </si>
+  <si>
+    <t>32,21</t>
+  </si>
+  <si>
+    <t>0,31</t>
+  </si>
+  <si>
+    <t>139,25</t>
+  </si>
+  <si>
+    <t>32,52</t>
+  </si>
+  <si>
+    <t>139,68</t>
+  </si>
+  <si>
+    <t>32,83</t>
+  </si>
+  <si>
+    <t>140,10</t>
+  </si>
+  <si>
+    <t>33,13</t>
+  </si>
+  <si>
+    <t>140,53</t>
+  </si>
+  <si>
+    <t>33,44</t>
+  </si>
+  <si>
+    <t>140,95</t>
+  </si>
+  <si>
+    <t>33,75</t>
+  </si>
+  <si>
+    <t>141,38</t>
+  </si>
+  <si>
+    <t>34,06</t>
+  </si>
+  <si>
+    <t>141,80</t>
+  </si>
+  <si>
+    <t>34,37</t>
+  </si>
+  <si>
+    <t>142,23</t>
+  </si>
+  <si>
+    <t>34,68</t>
+  </si>
+  <si>
+    <t>142,65</t>
+  </si>
+  <si>
+    <t>34,98</t>
+  </si>
+  <si>
+    <t>143,08</t>
+  </si>
+  <si>
+    <t>35,29</t>
+  </si>
+  <si>
+    <t>143,50</t>
+  </si>
+  <si>
+    <t>35,60</t>
+  </si>
+  <si>
+    <t>143,97</t>
+  </si>
+  <si>
+    <t>35,96</t>
+  </si>
+  <si>
+    <t>0,47</t>
+  </si>
+  <si>
+    <t>0,36</t>
+  </si>
+  <si>
+    <t>144,43</t>
+  </si>
+  <si>
+    <t>36,32</t>
+  </si>
+  <si>
+    <t>144,90</t>
+  </si>
+  <si>
+    <t>36,68</t>
+  </si>
+  <si>
+    <t>145,37</t>
+  </si>
+  <si>
+    <t>37,03</t>
+  </si>
+  <si>
+    <t>145,83</t>
+  </si>
+  <si>
+    <t>37,39</t>
+  </si>
+  <si>
+    <t>146,30</t>
+  </si>
+  <si>
+    <t>37,75</t>
+  </si>
+  <si>
+    <t>146,77</t>
+  </si>
+  <si>
+    <t>38,11</t>
+  </si>
+  <si>
+    <t>147,23</t>
+  </si>
+  <si>
+    <t>38,47</t>
+  </si>
+  <si>
+    <t>147,70</t>
+  </si>
+  <si>
+    <t>38,83</t>
+  </si>
+  <si>
+    <t>148,17</t>
+  </si>
+  <si>
+    <t>39,18</t>
+  </si>
+  <si>
+    <t>148,63</t>
+  </si>
+  <si>
+    <t>39,54</t>
+  </si>
+  <si>
+    <t>149,10</t>
+  </si>
+  <si>
+    <t>39,90</t>
+  </si>
+  <si>
+    <t>149,69</t>
+  </si>
+  <si>
+    <t>40,35</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>150,28</t>
+  </si>
+  <si>
+    <t>40,80</t>
+  </si>
+  <si>
+    <t>150,88</t>
+  </si>
+  <si>
+    <t>41,25</t>
+  </si>
+  <si>
+    <t>151,47</t>
+  </si>
+  <si>
+    <t>41,70</t>
+  </si>
+  <si>
+    <t>152,06</t>
+  </si>
+  <si>
+    <t>42,15</t>
+  </si>
+  <si>
+    <t>152,65</t>
+  </si>
+  <si>
+    <t>42,60</t>
+  </si>
+  <si>
+    <t>153,24</t>
+  </si>
+  <si>
+    <t>43,05</t>
+  </si>
+  <si>
+    <t>153,83</t>
+  </si>
+  <si>
+    <t>43,50</t>
+  </si>
+  <si>
+    <t>154,43</t>
+  </si>
+  <si>
+    <t>43,95</t>
+  </si>
+  <si>
+    <t>155,02</t>
+  </si>
+  <si>
+    <t>44,40</t>
+  </si>
+  <si>
+    <t>155,61</t>
+  </si>
+  <si>
+    <t>44,85</t>
+  </si>
+  <si>
+    <t>156,20</t>
+  </si>
+  <si>
+    <t>45,30</t>
+  </si>
+  <si>
+    <t>156,83</t>
+  </si>
+  <si>
+    <t>45,76</t>
+  </si>
+  <si>
+    <t>0,63</t>
+  </si>
+  <si>
+    <t>157,47</t>
+  </si>
+  <si>
+    <t>46,22</t>
+  </si>
+  <si>
+    <t>158,10</t>
+  </si>
+  <si>
+    <t>46,68</t>
+  </si>
+  <si>
+    <t>158,73</t>
+  </si>
+  <si>
+    <t>47,13</t>
+  </si>
+  <si>
+    <t>159,37</t>
+  </si>
+  <si>
+    <t>47,59</t>
+  </si>
+  <si>
+    <t>160,00</t>
+  </si>
+  <si>
+    <t>48,05</t>
+  </si>
+  <si>
+    <t>160,63</t>
+  </si>
+  <si>
+    <t>48,51</t>
+  </si>
+  <si>
+    <t>161,27</t>
+  </si>
+  <si>
+    <t>48,97</t>
+  </si>
+  <si>
+    <t>161,90</t>
+  </si>
+  <si>
+    <t>49,43</t>
+  </si>
+  <si>
+    <t>162,53</t>
+  </si>
+  <si>
+    <t>49,88</t>
+  </si>
+  <si>
+    <t>163,17</t>
+  </si>
+  <si>
+    <t>50,34</t>
+  </si>
+  <si>
+    <t>163,80</t>
+  </si>
+  <si>
+    <t>50,80</t>
+  </si>
+  <si>
+    <t>164,33</t>
+  </si>
+  <si>
+    <t>51,23</t>
+  </si>
+  <si>
+    <t>164,85</t>
+  </si>
+  <si>
+    <t>51,67</t>
+  </si>
+  <si>
+    <t>165,38</t>
+  </si>
+  <si>
+    <t>52,10</t>
+  </si>
+  <si>
+    <t>165,90</t>
+  </si>
+  <si>
+    <t>52,53</t>
+  </si>
+  <si>
+    <t>166,43</t>
+  </si>
+  <si>
+    <t>52,97</t>
+  </si>
+  <si>
+    <t>166,95</t>
+  </si>
+  <si>
+    <t>53,40</t>
+  </si>
+  <si>
+    <t>167,48</t>
+  </si>
+  <si>
+    <t>53,83</t>
+  </si>
+  <si>
+    <t>168,00</t>
+  </si>
+  <si>
+    <t>54,27</t>
+  </si>
+  <si>
+    <t>168,53</t>
+  </si>
+  <si>
+    <t>169,05</t>
+  </si>
+  <si>
+    <t>55,13</t>
+  </si>
+  <si>
+    <t>169,58</t>
+  </si>
+  <si>
+    <t>55,57</t>
+  </si>
+  <si>
+    <t>170,10</t>
+  </si>
+  <si>
+    <t>56,00</t>
+  </si>
+  <si>
+    <t>170,38</t>
+  </si>
+  <si>
+    <t>56,40</t>
+  </si>
+  <si>
+    <t>0,40</t>
+  </si>
+  <si>
+    <t>170,65</t>
+  </si>
+  <si>
+    <t>56,80</t>
+  </si>
+  <si>
+    <t>170,93</t>
+  </si>
+  <si>
+    <t>57,20</t>
+  </si>
+  <si>
+    <t>171,20</t>
+  </si>
+  <si>
+    <t>57,60</t>
+  </si>
+  <si>
+    <t>171,48</t>
+  </si>
+  <si>
+    <t>58,00</t>
+  </si>
+  <si>
+    <t>171,75</t>
+  </si>
+  <si>
+    <t>58,40</t>
+  </si>
+  <si>
+    <t>172,03</t>
+  </si>
+  <si>
+    <t>58,80</t>
+  </si>
+  <si>
+    <t>172,30</t>
+  </si>
+  <si>
+    <t>59,20</t>
+  </si>
+  <si>
+    <t>172,58</t>
+  </si>
+  <si>
+    <t>59,60</t>
+  </si>
+  <si>
+    <t>172,85</t>
+  </si>
+  <si>
+    <t>60,00</t>
+  </si>
+  <si>
+    <t>173,13</t>
+  </si>
+  <si>
+    <t>60,40</t>
+  </si>
+  <si>
+    <t>173,40</t>
+  </si>
+  <si>
+    <t>60,80</t>
+  </si>
+  <si>
+    <t>173,55</t>
+  </si>
+  <si>
+    <t>61,10</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>0,30</t>
+  </si>
+  <si>
+    <t>173,70</t>
+  </si>
+  <si>
+    <t>61,40</t>
+  </si>
+  <si>
+    <t>173,85</t>
+  </si>
+  <si>
+    <t>61,70</t>
+  </si>
+  <si>
+    <t>174,00</t>
+  </si>
+  <si>
+    <t>62,00</t>
+  </si>
+  <si>
+    <t>174,15</t>
+  </si>
+  <si>
+    <t>62,30</t>
+  </si>
+  <si>
+    <t>174,30</t>
+  </si>
+  <si>
+    <t>62,60</t>
+  </si>
+  <si>
+    <t>174,45</t>
+  </si>
+  <si>
+    <t>62,90</t>
+  </si>
+  <si>
+    <t>174,60</t>
+  </si>
+  <si>
+    <t>63,20</t>
+  </si>
+  <si>
+    <t>174,75</t>
+  </si>
+  <si>
+    <t>63,50</t>
+  </si>
+  <si>
+    <t>174,90</t>
+  </si>
+  <si>
+    <t>63,80</t>
+  </si>
+  <si>
+    <t>175,05</t>
+  </si>
+  <si>
+    <t>64,10</t>
+  </si>
+  <si>
+    <t>175,20</t>
+  </si>
+  <si>
+    <t>64,40</t>
+  </si>
+  <si>
+    <t>175,31</t>
+  </si>
+  <si>
+    <t>64,61</t>
+  </si>
+  <si>
+    <t>0,11</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>175,42</t>
+  </si>
+  <si>
+    <t>64,82</t>
+  </si>
+  <si>
+    <t>175,53</t>
+  </si>
+  <si>
+    <t>65,03</t>
+  </si>
+  <si>
+    <t>175,63</t>
+  </si>
+  <si>
+    <t>65,23</t>
+  </si>
+  <si>
+    <t>175,74</t>
+  </si>
+  <si>
+    <t>65,44</t>
+  </si>
+  <si>
+    <t>175,85</t>
+  </si>
+  <si>
+    <t>65,65</t>
+  </si>
+  <si>
+    <t>175,96</t>
+  </si>
+  <si>
+    <t>65,86</t>
+  </si>
+  <si>
+    <t>176,07</t>
+  </si>
+  <si>
+    <t>66,07</t>
+  </si>
+  <si>
+    <t>176,18</t>
+  </si>
+  <si>
+    <t>66,28</t>
+  </si>
+  <si>
+    <t>176,28</t>
+  </si>
+  <si>
+    <t>66,48</t>
+  </si>
+  <si>
+    <t>176,39</t>
+  </si>
+  <si>
+    <t>66,69</t>
+  </si>
+  <si>
+    <t>176,50</t>
+  </si>
+  <si>
+    <t>66,90</t>
+  </si>
+  <si>
+    <t>176,54</t>
+  </si>
+  <si>
+    <t>67,07</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>176,58</t>
+  </si>
+  <si>
+    <t>67,23</t>
+  </si>
+  <si>
+    <t>176,63</t>
+  </si>
+  <si>
+    <t>67,40</t>
+  </si>
+  <si>
+    <t>176,67</t>
+  </si>
+  <si>
+    <t>67,57</t>
+  </si>
+  <si>
+    <t>176,71</t>
+  </si>
+  <si>
+    <t>67,73</t>
+  </si>
+  <si>
+    <t>176,75</t>
+  </si>
+  <si>
+    <t>67,90</t>
+  </si>
+  <si>
+    <t>176,79</t>
+  </si>
+  <si>
+    <t>68,07</t>
+  </si>
+  <si>
+    <t>176,83</t>
+  </si>
+  <si>
+    <t>68,23</t>
+  </si>
+  <si>
+    <t>176,88</t>
+  </si>
+  <si>
+    <t>68,40</t>
+  </si>
+  <si>
+    <t>176,92</t>
+  </si>
+  <si>
+    <t>68,57</t>
+  </si>
+  <si>
+    <t>176,96</t>
+  </si>
+  <si>
+    <t>68,73</t>
+  </si>
+  <si>
+    <t>177,00</t>
+  </si>
+  <si>
+    <t>68,90</t>
   </si>
 </sst>
 </file>
@@ -1703,7 +1949,7 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
         <color rgb="FFCCCCCC"/>
@@ -1721,7 +1967,7 @@
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="medium">
         <color rgb="FF000000"/>
@@ -2039,7 +2285,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2064,8 +2310,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
@@ -2073,14 +2319,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
@@ -2088,14 +2331,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2670,10 +2910,10 @@
       <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="8"/>
+      <c r="E2" s="9"/>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="15.15" spans="1:6">
@@ -2686,13 +2926,13 @@
       <c r="C3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2706,13 +2946,13 @@
       <c r="C4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="12" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2726,13 +2966,13 @@
       <c r="C5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="12" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2746,13 +2986,13 @@
       <c r="C6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="12" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2766,13 +3006,13 @@
       <c r="C7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="12" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2786,13 +3026,13 @@
       <c r="C8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2804,16 +3044,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="11" t="s">
         <v>26</v>
       </c>
+      <c r="D9" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="E9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="13" t="s">
         <v>28</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="15.15" spans="1:6">
@@ -2824,16 +3064,16 @@
         <v>8</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="12" t="s">
         <v>29</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="11" ht="15.15" spans="1:6">
@@ -2846,14 +3086,14 @@
       <c r="C11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="13" t="s">
         <v>28</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="15.15" spans="1:6">
@@ -2866,14 +3106,14 @@
       <c r="C12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="13" t="s">
         <v>28</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="15.15" spans="1:6">
@@ -2886,14 +3126,14 @@
       <c r="C13" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>37</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="13" t="s">
         <v>28</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="15.15" spans="1:6">
@@ -2906,14 +3146,14 @@
       <c r="C14" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="13" t="s">
         <v>28</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="15.15" spans="1:6">
@@ -2924,16 +3164,16 @@
         <v>13</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="E15" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="F15" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="16" ht="15.15" spans="1:6">
@@ -2946,14 +3186,14 @@
       <c r="C16" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="12" t="s">
         <v>45</v>
       </c>
       <c r="E16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="17" ht="15.15" spans="1:6">
@@ -2966,14 +3206,14 @@
       <c r="C17" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="12" t="s">
         <v>47</v>
       </c>
       <c r="E17" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="18" ht="15.15" spans="1:6">
@@ -2984,16 +3224,16 @@
         <v>16</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="11" t="s">
         <v>48</v>
       </c>
+      <c r="D18" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="E18" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="19" ht="15.15" spans="1:6">
@@ -3004,16 +3244,16 @@
         <v>17</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="11" t="s">
         <v>50</v>
       </c>
+      <c r="D19" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="E19" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="20" ht="15.15" spans="1:6">
@@ -3024,16 +3264,16 @@
         <v>18</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="11" t="s">
         <v>52</v>
       </c>
+      <c r="D20" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="E20" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="21" ht="15.15" spans="1:6">
@@ -3044,16 +3284,16 @@
         <v>19</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="11" t="s">
         <v>54</v>
       </c>
+      <c r="D21" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="E21" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="22" ht="15.15" spans="1:6">
@@ -3064,16 +3304,16 @@
         <v>20</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="11" t="s">
         <v>56</v>
       </c>
+      <c r="D22" s="12" t="s">
+        <v>57</v>
+      </c>
       <c r="E22" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="23" ht="15.15" spans="1:6">
@@ -3084,16 +3324,16 @@
         <v>21</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="11" t="s">
         <v>58</v>
       </c>
+      <c r="D23" s="12" t="s">
+        <v>59</v>
+      </c>
       <c r="E23" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="24" ht="15.15" spans="1:6">
@@ -3104,16 +3344,16 @@
         <v>22</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="E24" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="25" ht="15.15" spans="1:6">
@@ -3124,16 +3364,16 @@
         <v>23</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="E25" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="26" ht="15.15" spans="1:6">
@@ -3144,16 +3384,16 @@
         <v>24</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>31</v>
+        <v>42</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="27" ht="15.15" spans="1:6">
@@ -3164,16 +3404,16 @@
         <v>25</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>31</v>
+        <v>68</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="28" ht="15.15" spans="1:6">
@@ -3184,16 +3424,16 @@
         <v>26</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E28" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>31</v>
+      <c r="F28" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="29" ht="15.15" spans="1:6">
@@ -3204,16 +3444,16 @@
         <v>27</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="30" ht="15.15" spans="1:6">
@@ -3224,16 +3464,16 @@
         <v>28</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>75</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>31</v>
+        <v>68</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="31" ht="15.15" spans="1:6">
@@ -3244,16 +3484,16 @@
         <v>29</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>77</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>31</v>
+        <v>68</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="32" ht="15.15" spans="1:6">
@@ -3264,16 +3504,16 @@
         <v>30</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>74</v>
+        <v>78</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>31</v>
+        <v>68</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="33" ht="15.15" spans="1:6">
@@ -3284,16 +3524,16 @@
         <v>31</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>81</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>31</v>
+        <v>68</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="34" ht="15.15" spans="1:6">
@@ -3304,16 +3544,16 @@
         <v>32</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>77</v>
+        <v>82</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>31</v>
+        <v>68</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="35" ht="15.15" spans="1:6">
@@ -3324,16 +3564,16 @@
         <v>33</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>79</v>
+        <v>84</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>31</v>
+        <v>68</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="36" ht="15.15" spans="1:6">
@@ -3344,16 +3584,16 @@
         <v>34</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>80</v>
+        <v>86</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>87</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>31</v>
+        <v>68</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="37" ht="15.15" spans="1:6">
@@ -3364,16 +3604,16 @@
         <v>35</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>82</v>
+        <v>88</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>31</v>
+        <v>68</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="38" ht="15.15" spans="1:6">
@@ -3384,16 +3624,16 @@
         <v>36</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>84</v>
+        <v>90</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>91</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>31</v>
+        <v>68</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="39" ht="15.15" spans="1:6">
@@ -3404,16 +3644,16 @@
         <v>37</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>94</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>31</v>
+        <v>95</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="40" ht="15.15" spans="1:6">
@@ -3424,16 +3664,16 @@
         <v>38</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>88</v>
+        <v>96</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>97</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>31</v>
+        <v>95</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="41" ht="15.15" spans="1:6">
@@ -3444,16 +3684,16 @@
         <v>39</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>91</v>
+        <v>98</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>31</v>
+        <v>95</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="42" ht="15.15" spans="1:6">
@@ -3464,16 +3704,16 @@
         <v>40</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D42" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F42" s="12" t="s">
         <v>92</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="43" ht="15.15" spans="1:6">
@@ -3484,16 +3724,16 @@
         <v>41</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>93</v>
+        <v>102</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>31</v>
+        <v>95</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="44" ht="15.15" spans="1:6">
@@ -3504,16 +3744,16 @@
         <v>42</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D44" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E44" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>31</v>
+      <c r="F44" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="45" ht="15.15" spans="1:6">
@@ -3524,16 +3764,16 @@
         <v>43</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>96</v>
+        <v>106</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>107</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>31</v>
+        <v>95</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="46" ht="15.15" spans="1:6">
@@ -3544,16 +3784,16 @@
         <v>44</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>98</v>
+        <v>108</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F46" s="13" t="s">
-        <v>31</v>
+        <v>95</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="47" ht="15.15" spans="1:6">
@@ -3564,16 +3804,16 @@
         <v>45</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>99</v>
+        <v>110</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>31</v>
+        <v>95</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="48" ht="15.15" spans="1:6">
@@ -3584,16 +3824,16 @@
         <v>46</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>101</v>
+        <v>112</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>113</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>31</v>
+        <v>95</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="49" ht="15.15" spans="1:6">
@@ -3604,16 +3844,16 @@
         <v>47</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>102</v>
+        <v>114</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>31</v>
+        <v>95</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="50" ht="15.15" spans="1:6">
@@ -3624,16 +3864,16 @@
         <v>48</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>104</v>
+        <v>116</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>31</v>
+        <v>95</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="51" ht="15.15" spans="1:6">
@@ -3644,16 +3884,16 @@
         <v>49</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>107</v>
+        <v>118</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>31</v>
+        <v>120</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="52" ht="15.15" spans="1:6">
@@ -3664,16 +3904,16 @@
         <v>50</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>109</v>
+        <v>121</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F52" s="13" t="s">
-        <v>31</v>
+        <v>120</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="53" ht="15.15" spans="1:6">
@@ -3684,16 +3924,16 @@
         <v>51</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>110</v>
+        <v>123</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F53" s="13" t="s">
-        <v>31</v>
+        <v>120</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="54" ht="15.15" spans="1:6">
@@ -3704,16 +3944,16 @@
         <v>52</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>112</v>
+        <v>125</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>31</v>
+        <v>120</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="55" ht="15.15" spans="1:6">
@@ -3724,16 +3964,16 @@
         <v>53</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>113</v>
+        <v>127</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F55" s="13" t="s">
-        <v>31</v>
+        <v>120</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="56" ht="15.15" spans="1:6">
@@ -3744,16 +3984,16 @@
         <v>54</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>115</v>
+        <v>129</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>31</v>
+        <v>120</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="57" ht="15.15" spans="1:6">
@@ -3764,16 +4004,16 @@
         <v>55</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>116</v>
+        <v>131</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>132</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F57" s="13" t="s">
-        <v>31</v>
+        <v>120</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="58" ht="15.15" spans="1:6">
@@ -3784,16 +4024,16 @@
         <v>56</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>118</v>
+        <v>133</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F58" s="13" t="s">
-        <v>31</v>
+        <v>120</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="59" ht="15.15" spans="1:6">
@@ -3804,16 +4044,16 @@
         <v>57</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>119</v>
+        <v>135</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F59" s="13" t="s">
-        <v>31</v>
+        <v>120</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="60" ht="15.15" spans="1:6">
@@ -3824,16 +4064,16 @@
         <v>58</v>
       </c>
       <c r="C60" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E60" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D60" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F60" s="13" t="s">
-        <v>31</v>
+      <c r="F60" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="61" ht="15.15" spans="1:6">
@@ -3844,16 +4084,16 @@
         <v>59</v>
       </c>
       <c r="C61" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E61" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D61" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F61" s="13" t="s">
-        <v>31</v>
+      <c r="F61" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="62" ht="15.15" spans="1:6">
@@ -3864,16 +4104,16 @@
         <v>60</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>124</v>
+        <v>141</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>142</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="F62" s="13" t="s">
-        <v>31</v>
+        <v>120</v>
+      </c>
+      <c r="F62" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="63" ht="15.15" spans="1:6">
@@ -3884,16 +4124,16 @@
         <v>61</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>127</v>
+        <v>143</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>144</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F63" s="13" t="s">
-        <v>31</v>
+        <v>145</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="64" ht="15.15" spans="1:6">
@@ -3904,16 +4144,16 @@
         <v>62</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>128</v>
+        <v>146</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F64" s="13" t="s">
-        <v>31</v>
+        <v>145</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="65" ht="15.15" spans="1:6">
@@ -3924,16 +4164,16 @@
         <v>63</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>129</v>
+        <v>148</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>149</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F65" s="13" t="s">
-        <v>31</v>
+        <v>145</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="66" ht="15.15" spans="1:6">
@@ -3944,16 +4184,16 @@
         <v>64</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>131</v>
+        <v>150</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F66" s="13" t="s">
-        <v>31</v>
+        <v>145</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="67" ht="15.15" spans="1:6">
@@ -3964,16 +4204,16 @@
         <v>65</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>132</v>
+        <v>152</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>153</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F67" s="13" t="s">
-        <v>31</v>
+        <v>145</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="68" ht="15.15" spans="1:6">
@@ -3984,16 +4224,16 @@
         <v>66</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>134</v>
+        <v>154</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>155</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F68" s="13" t="s">
-        <v>31</v>
+        <v>145</v>
+      </c>
+      <c r="F68" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="69" ht="15.15" spans="1:6">
@@ -4004,16 +4244,16 @@
         <v>67</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>135</v>
+        <v>156</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F69" s="13" t="s">
-        <v>31</v>
+        <v>145</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="70" ht="15.15" spans="1:6">
@@ -4024,16 +4264,16 @@
         <v>68</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>136</v>
+        <v>158</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>159</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F70" s="13" t="s">
-        <v>31</v>
+        <v>145</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="71" ht="15.15" spans="1:6">
@@ -4044,16 +4284,16 @@
         <v>69</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>138</v>
+        <v>160</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>161</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F71" s="13" t="s">
-        <v>31</v>
+        <v>145</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="72" ht="15.15" spans="1:6">
@@ -4064,16 +4304,16 @@
         <v>70</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="D72" s="11" t="s">
-        <v>139</v>
+        <v>162</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>163</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F72" s="13" t="s">
-        <v>31</v>
+        <v>145</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="73" ht="15.15" spans="1:6">
@@ -4084,16 +4324,16 @@
         <v>71</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>140</v>
+        <v>164</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>165</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F73" s="13" t="s">
-        <v>31</v>
+        <v>145</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="74" ht="15.15" spans="1:6">
@@ -4104,16 +4344,16 @@
         <v>72</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>142</v>
+        <v>166</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" s="13" t="s">
-        <v>31</v>
+        <v>145</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="75" ht="15.15" spans="1:6">
@@ -4124,16 +4364,16 @@
         <v>73</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D75" s="11" t="s">
-        <v>144</v>
+        <v>168</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F75" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="76" ht="15.15" spans="1:6">
@@ -4144,16 +4384,16 @@
         <v>74</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>145</v>
+        <v>171</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F76" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="77" ht="15.15" spans="1:6">
@@ -4164,16 +4404,16 @@
         <v>75</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="D77" s="11" t="s">
-        <v>147</v>
+        <v>172</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F77" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="78" ht="15.15" spans="1:6">
@@ -4184,16 +4424,16 @@
         <v>76</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="D78" s="11" t="s">
-        <v>148</v>
+        <v>173</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F78" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="79" ht="15.15" spans="1:6">
@@ -4204,16 +4444,16 @@
         <v>77</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>150</v>
+        <v>174</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F79" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="80" ht="15.15" spans="1:6">
@@ -4224,16 +4464,16 @@
         <v>78</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D80" s="11" t="s">
-        <v>151</v>
+        <v>175</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F80" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F80" s="12" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="81" ht="15.15" spans="1:6">
@@ -4244,16 +4484,16 @@
         <v>79</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D81" s="11" t="s">
-        <v>152</v>
+        <v>176</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F81" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="82" ht="15.15" spans="1:6">
@@ -4264,16 +4504,16 @@
         <v>80</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="D82" s="11" t="s">
-        <v>154</v>
+        <v>177</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F82" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="83" ht="15.15" spans="1:6">
@@ -4284,16 +4524,16 @@
         <v>81</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="D83" s="11" t="s">
-        <v>155</v>
+        <v>178</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F83" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F83" s="12" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="84" ht="15.15" spans="1:6">
@@ -4304,16 +4544,16 @@
         <v>82</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D84" s="11" t="s">
-        <v>157</v>
+        <v>179</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F84" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F84" s="12" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="85" ht="15.15" spans="1:6">
@@ -4324,16 +4564,16 @@
         <v>83</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D85" s="11" t="s">
-        <v>158</v>
+        <v>180</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F85" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="86" ht="15.15" spans="1:6">
@@ -4344,16 +4584,16 @@
         <v>84</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="D86" s="11" t="s">
-        <v>160</v>
+        <v>181</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>182</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F86" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F86" s="12" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="87" ht="15.15" spans="1:6">
@@ -4364,16 +4604,16 @@
         <v>85</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>162</v>
+        <v>184</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F87" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F87" s="12" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="88" ht="15.15" spans="1:6">
@@ -4384,16 +4624,16 @@
         <v>86</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="D88" s="11" t="s">
-        <v>165</v>
+        <v>187</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F88" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F88" s="12" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="89" ht="15.15" spans="1:6">
@@ -4404,16 +4644,16 @@
         <v>87</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="D89" s="11" t="s">
-        <v>167</v>
+        <v>189</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>190</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F89" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F89" s="12" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="90" ht="15.15" spans="1:6">
@@ -4424,16 +4664,16 @@
         <v>88</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="D90" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E90" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="E90" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F90" s="13" t="s">
-        <v>31</v>
+      <c r="F90" s="12" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="91" ht="15.15" spans="1:6">
@@ -4444,16 +4684,16 @@
         <v>89</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D91" s="11" t="s">
-        <v>171</v>
+        <v>193</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>194</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F91" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="92" ht="15.15" spans="1:6">
@@ -4464,16 +4704,16 @@
         <v>90</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D92" s="11" t="s">
-        <v>173</v>
+        <v>195</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>196</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F92" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F92" s="12" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="93" ht="15.15" spans="1:6">
@@ -4484,16 +4724,16 @@
         <v>91</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="D93" s="11" t="s">
-        <v>175</v>
+        <v>197</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>198</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F93" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="94" ht="15.15" spans="1:6">
@@ -4504,16 +4744,16 @@
         <v>92</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="D94" s="11" t="s">
-        <v>177</v>
+        <v>199</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>200</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F94" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F94" s="12" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="95" ht="15.15" spans="1:6">
@@ -4524,16 +4764,16 @@
         <v>93</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D95" s="11" t="s">
-        <v>179</v>
+        <v>201</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>202</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F95" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="96" ht="15.15" spans="1:6">
@@ -4544,16 +4784,16 @@
         <v>94</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="D96" s="11" t="s">
-        <v>181</v>
+        <v>203</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>204</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F96" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F96" s="12" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="97" ht="15.15" spans="1:6">
@@ -4564,16 +4804,16 @@
         <v>95</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D97" s="11" t="s">
-        <v>183</v>
+        <v>205</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F97" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F97" s="12" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="98" ht="15.15" spans="1:6">
@@ -4584,16 +4824,16 @@
         <v>96</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>185</v>
+        <v>207</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>208</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F98" s="13" t="s">
-        <v>31</v>
+        <v>209</v>
+      </c>
+      <c r="F98" s="12" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="99" ht="15.15" spans="1:6">
@@ -4604,16 +4844,16 @@
         <v>97</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D99" s="11" t="s">
-        <v>187</v>
+        <v>210</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F99" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F99" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="100" ht="15.15" spans="1:6">
@@ -4624,16 +4864,16 @@
         <v>98</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="D100" s="11" t="s">
-        <v>189</v>
+        <v>214</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F100" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F100" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="101" ht="15.15" spans="1:6">
@@ -4644,16 +4884,16 @@
         <v>99</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="D101" s="11" t="s">
-        <v>191</v>
+        <v>216</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>217</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F101" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F101" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="102" ht="15.15" spans="1:6">
@@ -4664,16 +4904,16 @@
         <v>100</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D102" s="11" t="s">
-        <v>193</v>
+        <v>218</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>219</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F102" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F102" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="103" ht="15.15" spans="1:6">
@@ -4684,16 +4924,16 @@
         <v>101</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="D103" s="11" t="s">
-        <v>195</v>
+        <v>220</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F103" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F103" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="104" ht="15.15" spans="1:6">
@@ -4704,16 +4944,16 @@
         <v>102</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="D104" s="11" t="s">
-        <v>197</v>
+        <v>222</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F104" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F104" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="105" ht="15.15" spans="1:6">
@@ -4724,16 +4964,16 @@
         <v>103</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="D105" s="11" t="s">
-        <v>199</v>
+        <v>224</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>225</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F105" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F105" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="106" ht="15.15" spans="1:6">
@@ -4744,16 +4984,16 @@
         <v>104</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="D106" s="11" t="s">
-        <v>201</v>
+        <v>226</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>227</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F106" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F106" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="107" ht="15.15" spans="1:6">
@@ -4764,16 +5004,16 @@
         <v>105</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="D107" s="11" t="s">
-        <v>203</v>
+        <v>228</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>229</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F107" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F107" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="108" ht="15.15" spans="1:6">
@@ -4784,16 +5024,16 @@
         <v>106</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="D108" s="11" t="s">
-        <v>205</v>
+        <v>230</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F108" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F108" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="109" ht="15.15" spans="1:6">
@@ -4804,16 +5044,16 @@
         <v>107</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="D109" s="11" t="s">
-        <v>207</v>
+        <v>232</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>233</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F109" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F109" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="110" ht="15.15" spans="1:6">
@@ -4824,16 +5064,16 @@
         <v>108</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="D110" s="11" t="s">
-        <v>209</v>
+        <v>234</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>235</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F110" s="13" t="s">
-        <v>28</v>
+        <v>236</v>
+      </c>
+      <c r="F110" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="111" ht="15.15" spans="1:6">
@@ -4844,16 +5084,16 @@
         <v>109</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>211</v>
+        <v>237</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>238</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F111" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F111" s="12" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="112" ht="15.15" spans="1:6">
@@ -4864,16 +5104,16 @@
         <v>110</v>
       </c>
       <c r="C112" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="E112" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="D112" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="E112" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F112" s="13" t="s">
-        <v>28</v>
+      <c r="F112" s="12" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="113" ht="15.15" spans="1:6">
@@ -4884,16 +5124,16 @@
         <v>111</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="D113" s="11" t="s">
-        <v>215</v>
+        <v>242</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>243</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F113" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F113" s="12" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="114" ht="15.15" spans="1:6">
@@ -4904,16 +5144,16 @@
         <v>112</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="D114" s="11" t="s">
-        <v>217</v>
+        <v>244</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>245</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F114" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F114" s="12" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="115" ht="15.15" spans="1:6">
@@ -4924,16 +5164,16 @@
         <v>113</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="D115" s="11" t="s">
-        <v>219</v>
+        <v>246</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>247</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F115" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F115" s="12" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="116" ht="15.15" spans="1:6">
@@ -4944,16 +5184,16 @@
         <v>114</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="D116" s="11" t="s">
-        <v>221</v>
+        <v>248</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>249</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F116" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F116" s="12" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="117" ht="15.15" spans="1:6">
@@ -4964,16 +5204,16 @@
         <v>115</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="D117" s="11" t="s">
-        <v>223</v>
+        <v>250</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>251</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F117" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F117" s="12" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="118" ht="15.15" spans="1:6">
@@ -4984,16 +5224,16 @@
         <v>116</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="D118" s="11" t="s">
-        <v>225</v>
+        <v>252</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>253</v>
       </c>
       <c r="E118" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F118" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F118" s="12" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="119" ht="15.15" spans="1:6">
@@ -5004,16 +5244,16 @@
         <v>117</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>227</v>
+        <v>254</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>255</v>
       </c>
       <c r="E119" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F119" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F119" s="12" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="120" ht="15.15" spans="1:6">
@@ -5024,16 +5264,16 @@
         <v>118</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="D120" s="11" t="s">
-        <v>229</v>
+        <v>256</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>257</v>
       </c>
       <c r="E120" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F120" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F120" s="12" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="121" ht="15.15" spans="1:6">
@@ -5044,16 +5284,16 @@
         <v>119</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="D121" s="11" t="s">
-        <v>231</v>
+        <v>258</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>259</v>
       </c>
       <c r="E121" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F121" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F121" s="12" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="122" ht="15.15" spans="1:6">
@@ -5064,16 +5304,16 @@
         <v>120</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="D122" s="11" t="s">
-        <v>233</v>
+        <v>260</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>261</v>
       </c>
       <c r="E122" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F122" s="13" t="s">
-        <v>28</v>
+        <v>236</v>
+      </c>
+      <c r="F122" s="12" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="123" ht="15.15" spans="1:6">
@@ -5084,16 +5324,16 @@
         <v>121</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="D123" s="11" t="s">
-        <v>235</v>
+        <v>262</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="E123" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F123" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F123" s="12" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="124" ht="15.15" spans="1:6">
@@ -5104,16 +5344,16 @@
         <v>122</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="D124" s="11" t="s">
-        <v>237</v>
+        <v>265</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>266</v>
       </c>
       <c r="E124" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F124" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F124" s="12" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="125" ht="15.15" spans="1:6">
@@ -5124,16 +5364,16 @@
         <v>123</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="D125" s="11" t="s">
-        <v>239</v>
+        <v>267</v>
+      </c>
+      <c r="D125" s="12" t="s">
+        <v>268</v>
       </c>
       <c r="E125" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F125" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F125" s="12" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="126" ht="15.15" spans="1:6">
@@ -5144,16 +5384,16 @@
         <v>124</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="D126" s="11" t="s">
-        <v>241</v>
+        <v>269</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>270</v>
       </c>
       <c r="E126" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F126" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F126" s="12" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="127" ht="15.15" spans="1:6">
@@ -5164,16 +5404,16 @@
         <v>125</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="D127" s="11" t="s">
-        <v>243</v>
+        <v>271</v>
+      </c>
+      <c r="D127" s="12" t="s">
+        <v>272</v>
       </c>
       <c r="E127" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F127" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F127" s="12" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="128" ht="15.15" spans="1:6">
@@ -5184,16 +5424,16 @@
         <v>126</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="D128" s="11" t="s">
-        <v>245</v>
+        <v>273</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>274</v>
       </c>
       <c r="E128" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F128" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F128" s="12" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="129" ht="15.15" spans="1:6">
@@ -5204,16 +5444,16 @@
         <v>127</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="D129" s="11" t="s">
-        <v>247</v>
+        <v>275</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>276</v>
       </c>
       <c r="E129" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F129" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F129" s="12" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="130" ht="15.15" spans="1:6">
@@ -5224,16 +5464,16 @@
         <v>128</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="D130" s="11" t="s">
-        <v>249</v>
+        <v>277</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>278</v>
       </c>
       <c r="E130" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F130" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F130" s="12" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="131" ht="15.15" spans="1:6">
@@ -5244,16 +5484,16 @@
         <v>129</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="D131" s="11" t="s">
-        <v>251</v>
+        <v>279</v>
+      </c>
+      <c r="D131" s="12" t="s">
+        <v>280</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F131" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F131" s="12" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="132" ht="15.15" spans="1:6">
@@ -5264,16 +5504,16 @@
         <v>130</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="D132" s="11" t="s">
-        <v>253</v>
+        <v>281</v>
+      </c>
+      <c r="D132" s="12" t="s">
+        <v>282</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F132" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F132" s="12" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="133" ht="15.15" spans="1:6">
@@ -5284,16 +5524,16 @@
         <v>131</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="D133" s="11" t="s">
-        <v>255</v>
+        <v>283</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>284</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F133" s="13" t="s">
-        <v>28</v>
+        <v>212</v>
+      </c>
+      <c r="F133" s="12" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="134" ht="15.15" spans="1:6">
@@ -5304,16 +5544,16 @@
         <v>132</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="D134" s="11" t="s">
-        <v>257</v>
+        <v>285</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>286</v>
       </c>
       <c r="E134" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F134" s="13" t="s">
-        <v>28</v>
+        <v>236</v>
+      </c>
+      <c r="F134" s="12" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="135" ht="15.15" spans="1:6">
@@ -5324,16 +5564,16 @@
         <v>133</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="D135" s="11" t="s">
-        <v>259</v>
+        <v>287</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>288</v>
       </c>
       <c r="E135" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F135" s="13" t="s">
-        <v>163</v>
+        <v>289</v>
+      </c>
+      <c r="F135" s="12" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="136" ht="15.15" spans="1:6">
@@ -5344,16 +5584,16 @@
         <v>134</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="D136" s="11" t="s">
-        <v>261</v>
+        <v>291</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>292</v>
       </c>
       <c r="E136" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F136" s="13" t="s">
-        <v>163</v>
+        <v>289</v>
+      </c>
+      <c r="F136" s="12" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="137" ht="15.15" spans="1:6">
@@ -5364,16 +5604,16 @@
         <v>135</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="D137" s="11" t="s">
-        <v>263</v>
+        <v>293</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>294</v>
       </c>
       <c r="E137" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F137" s="13" t="s">
-        <v>163</v>
+        <v>289</v>
+      </c>
+      <c r="F137" s="12" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="138" ht="15.15" spans="1:6">
@@ -5384,16 +5624,16 @@
         <v>136</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="D138" s="11" t="s">
-        <v>265</v>
+        <v>295</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>296</v>
       </c>
       <c r="E138" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F138" s="13" t="s">
-        <v>163</v>
+        <v>289</v>
+      </c>
+      <c r="F138" s="12" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="139" ht="15.15" spans="1:6">
@@ -5404,16 +5644,16 @@
         <v>137</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="D139" s="11" t="s">
-        <v>267</v>
+        <v>297</v>
+      </c>
+      <c r="D139" s="12" t="s">
+        <v>298</v>
       </c>
       <c r="E139" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F139" s="13" t="s">
-        <v>163</v>
+        <v>289</v>
+      </c>
+      <c r="F139" s="12" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="140" ht="15.15" spans="1:6">
@@ -5424,16 +5664,16 @@
         <v>138</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="D140" s="11" t="s">
-        <v>269</v>
+        <v>299</v>
+      </c>
+      <c r="D140" s="12" t="s">
+        <v>300</v>
       </c>
       <c r="E140" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F140" s="13" t="s">
-        <v>163</v>
+        <v>289</v>
+      </c>
+      <c r="F140" s="12" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="141" ht="15.15" spans="1:6">
@@ -5444,16 +5684,16 @@
         <v>139</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="D141" s="11" t="s">
-        <v>271</v>
+        <v>301</v>
+      </c>
+      <c r="D141" s="12" t="s">
+        <v>302</v>
       </c>
       <c r="E141" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F141" s="13" t="s">
-        <v>163</v>
+        <v>289</v>
+      </c>
+      <c r="F141" s="12" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="142" ht="15.15" spans="1:6">
@@ -5464,16 +5704,16 @@
         <v>140</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="D142" s="11" t="s">
-        <v>273</v>
+        <v>303</v>
+      </c>
+      <c r="D142" s="12" t="s">
+        <v>304</v>
       </c>
       <c r="E142" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F142" s="13" t="s">
-        <v>163</v>
+        <v>289</v>
+      </c>
+      <c r="F142" s="12" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="143" ht="15.15" spans="1:6">
@@ -5484,16 +5724,16 @@
         <v>141</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="D143" s="11" t="s">
-        <v>275</v>
+        <v>305</v>
+      </c>
+      <c r="D143" s="12" t="s">
+        <v>306</v>
       </c>
       <c r="E143" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F143" s="13" t="s">
-        <v>163</v>
+        <v>289</v>
+      </c>
+      <c r="F143" s="12" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="144" ht="15.15" spans="1:6">
@@ -5504,16 +5744,16 @@
         <v>142</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="D144" s="11" t="s">
-        <v>277</v>
+        <v>307</v>
+      </c>
+      <c r="D144" s="12" t="s">
+        <v>308</v>
       </c>
       <c r="E144" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F144" s="13" t="s">
-        <v>163</v>
+        <v>289</v>
+      </c>
+      <c r="F144" s="12" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="145" ht="15.15" spans="1:6">
@@ -5524,16 +5764,16 @@
         <v>143</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="D145" s="11" t="s">
-        <v>279</v>
+        <v>309</v>
+      </c>
+      <c r="D145" s="12" t="s">
+        <v>310</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F145" s="13" t="s">
-        <v>163</v>
+        <v>289</v>
+      </c>
+      <c r="F145" s="12" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="146" ht="15.15" spans="1:6">
@@ -5544,16 +5784,16 @@
         <v>144</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="D146" s="11" t="s">
-        <v>281</v>
+        <v>311</v>
+      </c>
+      <c r="D146" s="12" t="s">
+        <v>312</v>
       </c>
       <c r="E146" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F146" s="13" t="s">
-        <v>163</v>
+        <v>289</v>
+      </c>
+      <c r="F146" s="12" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="147" ht="15.15" spans="1:6">
@@ -5564,16 +5804,16 @@
         <v>145</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="D147" s="11" t="s">
-        <v>283</v>
+        <v>313</v>
+      </c>
+      <c r="D147" s="12" t="s">
+        <v>314</v>
       </c>
       <c r="E147" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F147" s="13" t="s">
-        <v>163</v>
+        <v>120</v>
+      </c>
+      <c r="F147" s="12" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="148" ht="15.15" spans="1:6">
@@ -5584,16 +5824,16 @@
         <v>146</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="D148" s="11" t="s">
-        <v>285</v>
+        <v>316</v>
+      </c>
+      <c r="D148" s="12" t="s">
+        <v>317</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F148" s="13" t="s">
-        <v>163</v>
+        <v>120</v>
+      </c>
+      <c r="F148" s="12" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="149" ht="15.15" spans="1:6">
@@ -5604,16 +5844,16 @@
         <v>147</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="D149" s="11" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="D149" s="12" t="s">
+        <v>319</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F149" s="13" t="s">
-        <v>163</v>
+        <v>120</v>
+      </c>
+      <c r="F149" s="12" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="150" ht="15.15" spans="1:6">
@@ -5624,16 +5864,16 @@
         <v>148</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="D150" s="11" t="s">
-        <v>289</v>
+        <v>320</v>
+      </c>
+      <c r="D150" s="12" t="s">
+        <v>321</v>
       </c>
       <c r="E150" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F150" s="13" t="s">
-        <v>163</v>
+        <v>120</v>
+      </c>
+      <c r="F150" s="12" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="151" ht="15.15" spans="1:6">
@@ -5644,16 +5884,16 @@
         <v>149</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="D151" s="11" t="s">
-        <v>291</v>
+        <v>322</v>
+      </c>
+      <c r="D151" s="12" t="s">
+        <v>323</v>
       </c>
       <c r="E151" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F151" s="13" t="s">
-        <v>163</v>
+        <v>120</v>
+      </c>
+      <c r="F151" s="12" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="152" ht="15.15" spans="1:6">
@@ -5664,16 +5904,16 @@
         <v>150</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="D152" s="11" t="s">
-        <v>293</v>
+        <v>324</v>
+      </c>
+      <c r="D152" s="12" t="s">
+        <v>325</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F152" s="13" t="s">
-        <v>163</v>
+        <v>120</v>
+      </c>
+      <c r="F152" s="12" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="153" ht="15.15" spans="1:6">
@@ -5684,16 +5924,16 @@
         <v>151</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="D153" s="11" t="s">
-        <v>295</v>
+        <v>326</v>
+      </c>
+      <c r="D153" s="12" t="s">
+        <v>327</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F153" s="13" t="s">
-        <v>163</v>
+        <v>120</v>
+      </c>
+      <c r="F153" s="12" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="154" ht="15.15" spans="1:6">
@@ -5704,16 +5944,16 @@
         <v>152</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="D154" s="11" t="s">
-        <v>297</v>
+        <v>328</v>
+      </c>
+      <c r="D154" s="12" t="s">
+        <v>329</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F154" s="13" t="s">
-        <v>163</v>
+        <v>120</v>
+      </c>
+      <c r="F154" s="12" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="155" ht="15.15" spans="1:6">
@@ -5724,16 +5964,16 @@
         <v>153</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="D155" s="11" t="s">
-        <v>299</v>
+        <v>330</v>
+      </c>
+      <c r="D155" s="12" t="s">
+        <v>331</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F155" s="13" t="s">
-        <v>163</v>
+        <v>120</v>
+      </c>
+      <c r="F155" s="12" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="156" ht="15.15" spans="1:6">
@@ -5744,16 +5984,16 @@
         <v>154</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="D156" s="11" t="s">
-        <v>301</v>
+        <v>332</v>
+      </c>
+      <c r="D156" s="12" t="s">
+        <v>333</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F156" s="13" t="s">
-        <v>163</v>
+        <v>120</v>
+      </c>
+      <c r="F156" s="12" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="157" ht="15.15" spans="1:6">
@@ -5764,16 +6004,16 @@
         <v>155</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="D157" s="11" t="s">
-        <v>303</v>
+        <v>334</v>
+      </c>
+      <c r="D157" s="12" t="s">
+        <v>335</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F157" s="13" t="s">
-        <v>163</v>
+        <v>120</v>
+      </c>
+      <c r="F157" s="12" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="158" ht="15.15" spans="1:6">
@@ -5784,16 +6024,16 @@
         <v>156</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="D158" s="11" t="s">
-        <v>305</v>
+        <v>336</v>
+      </c>
+      <c r="D158" s="12" t="s">
+        <v>337</v>
       </c>
       <c r="E158" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F158" s="13" t="s">
-        <v>163</v>
+        <v>120</v>
+      </c>
+      <c r="F158" s="12" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="159" ht="15.15" spans="1:6">
@@ -5804,16 +6044,16 @@
         <v>157</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>306</v>
-      </c>
-      <c r="D159" s="11" t="s">
-        <v>307</v>
+        <v>338</v>
+      </c>
+      <c r="D159" s="12" t="s">
+        <v>339</v>
       </c>
       <c r="E159" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F159" s="13" t="s">
-        <v>28</v>
+        <v>340</v>
+      </c>
+      <c r="F159" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="160" ht="15.15" spans="1:6">
@@ -5824,16 +6064,16 @@
         <v>158</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="D160" s="11" t="s">
-        <v>309</v>
+        <v>341</v>
+      </c>
+      <c r="D160" s="12" t="s">
+        <v>342</v>
       </c>
       <c r="E160" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F160" s="13" t="s">
-        <v>28</v>
+        <v>340</v>
+      </c>
+      <c r="F160" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="161" ht="15.15" spans="1:6">
@@ -5844,16 +6084,16 @@
         <v>159</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="D161" s="11" t="s">
-        <v>311</v>
+        <v>343</v>
+      </c>
+      <c r="D161" s="12" t="s">
+        <v>344</v>
       </c>
       <c r="E161" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F161" s="13" t="s">
-        <v>28</v>
+        <v>340</v>
+      </c>
+      <c r="F161" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="162" ht="15.15" spans="1:6">
@@ -5864,16 +6104,16 @@
         <v>160</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="D162" s="11" t="s">
-        <v>313</v>
+        <v>345</v>
+      </c>
+      <c r="D162" s="12" t="s">
+        <v>346</v>
       </c>
       <c r="E162" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F162" s="13" t="s">
-        <v>28</v>
+        <v>340</v>
+      </c>
+      <c r="F162" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="163" ht="15.15" spans="1:6">
@@ -5884,16 +6124,16 @@
         <v>161</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="D163" s="11" t="s">
-        <v>315</v>
+        <v>347</v>
+      </c>
+      <c r="D163" s="12" t="s">
+        <v>348</v>
       </c>
       <c r="E163" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F163" s="13" t="s">
-        <v>28</v>
+        <v>340</v>
+      </c>
+      <c r="F163" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="164" ht="15.15" spans="1:6">
@@ -5904,16 +6144,16 @@
         <v>162</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="D164" s="11" t="s">
-        <v>317</v>
+        <v>349</v>
+      </c>
+      <c r="D164" s="12" t="s">
+        <v>350</v>
       </c>
       <c r="E164" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F164" s="13" t="s">
-        <v>28</v>
+        <v>340</v>
+      </c>
+      <c r="F164" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="165" ht="15.15" spans="1:6">
@@ -5924,16 +6164,16 @@
         <v>163</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="D165" s="11" t="s">
-        <v>319</v>
+        <v>351</v>
+      </c>
+      <c r="D165" s="12" t="s">
+        <v>352</v>
       </c>
       <c r="E165" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F165" s="13" t="s">
-        <v>28</v>
+        <v>340</v>
+      </c>
+      <c r="F165" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="166" ht="15.15" spans="1:6">
@@ -5944,16 +6184,16 @@
         <v>164</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="D166" s="11" t="s">
-        <v>321</v>
+        <v>353</v>
+      </c>
+      <c r="D166" s="12" t="s">
+        <v>354</v>
       </c>
       <c r="E166" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F166" s="13" t="s">
-        <v>28</v>
+        <v>340</v>
+      </c>
+      <c r="F166" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="167" ht="15.15" spans="1:6">
@@ -5964,16 +6204,16 @@
         <v>165</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="D167" s="11" t="s">
-        <v>323</v>
+        <v>355</v>
+      </c>
+      <c r="D167" s="12" t="s">
+        <v>356</v>
       </c>
       <c r="E167" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F167" s="13" t="s">
-        <v>28</v>
+        <v>340</v>
+      </c>
+      <c r="F167" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="168" ht="15.15" spans="1:6">
@@ -5984,16 +6224,16 @@
         <v>166</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>324</v>
-      </c>
-      <c r="D168" s="11" t="s">
-        <v>325</v>
+        <v>357</v>
+      </c>
+      <c r="D168" s="12" t="s">
+        <v>358</v>
       </c>
       <c r="E168" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F168" s="13" t="s">
-        <v>28</v>
+        <v>340</v>
+      </c>
+      <c r="F168" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="169" ht="15.15" spans="1:6">
@@ -6004,16 +6244,16 @@
         <v>167</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="D169" s="11" t="s">
-        <v>327</v>
+        <v>359</v>
+      </c>
+      <c r="D169" s="12" t="s">
+        <v>360</v>
       </c>
       <c r="E169" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F169" s="13" t="s">
-        <v>28</v>
+        <v>340</v>
+      </c>
+      <c r="F169" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="170" ht="15.15" spans="1:6">
@@ -6024,16 +6264,16 @@
         <v>168</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="D170" s="11" t="s">
-        <v>329</v>
+        <v>361</v>
+      </c>
+      <c r="D170" s="12" t="s">
+        <v>362</v>
       </c>
       <c r="E170" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F170" s="13" t="s">
-        <v>28</v>
+        <v>340</v>
+      </c>
+      <c r="F170" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="171" ht="15.15" spans="1:6">
@@ -6044,16 +6284,16 @@
         <v>169</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="D171" s="11" t="s">
-        <v>331</v>
+        <v>363</v>
+      </c>
+      <c r="D171" s="12" t="s">
+        <v>364</v>
       </c>
       <c r="E171" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F171" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F171" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="172" ht="15.15" spans="1:6">
@@ -6064,16 +6304,16 @@
         <v>170</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="D172" s="11" t="s">
-        <v>333</v>
+        <v>365</v>
+      </c>
+      <c r="D172" s="12" t="s">
+        <v>366</v>
       </c>
       <c r="E172" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F172" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F172" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="173" ht="15.15" spans="1:6">
@@ -6084,16 +6324,16 @@
         <v>171</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="D173" s="11" t="s">
-        <v>335</v>
+        <v>367</v>
+      </c>
+      <c r="D173" s="12" t="s">
+        <v>368</v>
       </c>
       <c r="E173" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F173" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F173" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="174" ht="15.15" spans="1:6">
@@ -6104,16 +6344,16 @@
         <v>172</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="D174" s="11" t="s">
-        <v>337</v>
+        <v>369</v>
+      </c>
+      <c r="D174" s="12" t="s">
+        <v>370</v>
       </c>
       <c r="E174" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F174" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F174" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="175" ht="15.15" spans="1:6">
@@ -6124,16 +6364,16 @@
         <v>173</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="D175" s="11" t="s">
-        <v>339</v>
+        <v>371</v>
+      </c>
+      <c r="D175" s="12" t="s">
+        <v>372</v>
       </c>
       <c r="E175" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F175" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F175" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="176" ht="15.15" spans="1:6">
@@ -6144,16 +6384,16 @@
         <v>174</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="D176" s="11" t="s">
-        <v>341</v>
+        <v>373</v>
+      </c>
+      <c r="D176" s="12" t="s">
+        <v>374</v>
       </c>
       <c r="E176" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F176" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F176" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="177" ht="15.15" spans="1:6">
@@ -6164,16 +6404,16 @@
         <v>175</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="D177" s="11" t="s">
-        <v>343</v>
+        <v>375</v>
+      </c>
+      <c r="D177" s="12" t="s">
+        <v>376</v>
       </c>
       <c r="E177" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F177" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F177" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="178" ht="15.15" spans="1:6">
@@ -6184,16 +6424,16 @@
         <v>176</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="D178" s="11" t="s">
-        <v>345</v>
+        <v>377</v>
+      </c>
+      <c r="D178" s="12" t="s">
+        <v>378</v>
       </c>
       <c r="E178" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F178" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F178" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="179" ht="15.15" spans="1:6">
@@ -6204,16 +6444,16 @@
         <v>177</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="D179" s="11" t="s">
-        <v>347</v>
+        <v>379</v>
+      </c>
+      <c r="D179" s="12" t="s">
+        <v>8</v>
       </c>
       <c r="E179" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F179" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F179" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="180" ht="15.15" spans="1:6">
@@ -6224,16 +6464,16 @@
         <v>178</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="D180" s="11" t="s">
-        <v>349</v>
+        <v>380</v>
+      </c>
+      <c r="D180" s="12" t="s">
+        <v>381</v>
       </c>
       <c r="E180" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F180" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F180" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="181" ht="15.15" spans="1:6">
@@ -6244,16 +6484,16 @@
         <v>179</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="D181" s="11" t="s">
-        <v>351</v>
+        <v>382</v>
+      </c>
+      <c r="D181" s="12" t="s">
+        <v>383</v>
       </c>
       <c r="E181" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F181" s="13" t="s">
-        <v>31</v>
+        <v>169</v>
+      </c>
+      <c r="F181" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="182" ht="15.15" spans="1:6">
@@ -6264,16 +6504,16 @@
         <v>180</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="D182" s="11" t="s">
-        <v>353</v>
+        <v>384</v>
+      </c>
+      <c r="D182" s="12" t="s">
+        <v>385</v>
       </c>
       <c r="E182" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F182" s="13" t="s">
-        <v>31</v>
+        <v>209</v>
+      </c>
+      <c r="F182" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="183" ht="15.15" spans="1:6">
@@ -6284,16 +6524,16 @@
         <v>181</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>354</v>
-      </c>
-      <c r="D183" s="11" t="s">
-        <v>355</v>
+        <v>386</v>
+      </c>
+      <c r="D183" s="12" t="s">
+        <v>387</v>
       </c>
       <c r="E183" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F183" s="13" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="F183" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="184" ht="15.15" spans="1:6">
@@ -6304,16 +6544,16 @@
         <v>182</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="D184" s="11" t="s">
-        <v>357</v>
+        <v>389</v>
+      </c>
+      <c r="D184" s="12" t="s">
+        <v>390</v>
       </c>
       <c r="E184" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F184" s="13" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="F184" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="185" ht="15.15" spans="1:6">
@@ -6324,16 +6564,16 @@
         <v>183</v>
       </c>
       <c r="C185" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="D185" s="11" t="s">
-        <v>359</v>
+        <v>391</v>
+      </c>
+      <c r="D185" s="12" t="s">
+        <v>392</v>
       </c>
       <c r="E185" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F185" s="13" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="F185" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="186" ht="15.15" spans="1:6">
@@ -6344,16 +6584,16 @@
         <v>184</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="D186" s="11" t="s">
-        <v>361</v>
+        <v>393</v>
+      </c>
+      <c r="D186" s="12" t="s">
+        <v>394</v>
       </c>
       <c r="E186" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F186" s="13" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="F186" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="187" ht="15.15" spans="1:6">
@@ -6364,16 +6604,16 @@
         <v>185</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="D187" s="11" t="s">
-        <v>363</v>
+        <v>395</v>
+      </c>
+      <c r="D187" s="12" t="s">
+        <v>396</v>
       </c>
       <c r="E187" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F187" s="13" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="F187" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="188" ht="15.15" spans="1:6">
@@ -6384,16 +6624,16 @@
         <v>186</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="D188" s="11" t="s">
-        <v>365</v>
+        <v>397</v>
+      </c>
+      <c r="D188" s="12" t="s">
+        <v>398</v>
       </c>
       <c r="E188" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F188" s="13" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="F188" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="189" ht="15.15" spans="1:6">
@@ -6404,16 +6644,16 @@
         <v>187</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="D189" s="11" t="s">
-        <v>367</v>
+        <v>399</v>
+      </c>
+      <c r="D189" s="12" t="s">
+        <v>400</v>
       </c>
       <c r="E189" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F189" s="13" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="F189" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="190" ht="15.15" spans="1:6">
@@ -6424,16 +6664,16 @@
         <v>188</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="D190" s="11" t="s">
-        <v>369</v>
+        <v>401</v>
+      </c>
+      <c r="D190" s="12" t="s">
+        <v>402</v>
       </c>
       <c r="E190" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F190" s="13" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="F190" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="191" ht="15.15" spans="1:6">
@@ -6444,16 +6684,16 @@
         <v>189</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="D191" s="11" t="s">
-        <v>371</v>
+        <v>403</v>
+      </c>
+      <c r="D191" s="12" t="s">
+        <v>404</v>
       </c>
       <c r="E191" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F191" s="13" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="F191" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="192" ht="15.15" spans="1:6">
@@ -6464,16 +6704,16 @@
         <v>190</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="D192" s="11" t="s">
-        <v>373</v>
+        <v>405</v>
+      </c>
+      <c r="D192" s="12" t="s">
+        <v>406</v>
       </c>
       <c r="E192" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F192" s="13" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="F192" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="193" ht="15.15" spans="1:6">
@@ -6484,16 +6724,16 @@
         <v>191</v>
       </c>
       <c r="C193" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="D193" s="11" t="s">
-        <v>375</v>
+        <v>407</v>
+      </c>
+      <c r="D193" s="12" t="s">
+        <v>408</v>
       </c>
       <c r="E193" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F193" s="13" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="F193" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="194" ht="15.15" spans="1:6">
@@ -6504,16 +6744,16 @@
         <v>192</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D194" s="11" t="s">
-        <v>377</v>
+        <v>409</v>
+      </c>
+      <c r="D194" s="12" t="s">
+        <v>410</v>
       </c>
       <c r="E194" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F194" s="13" t="s">
-        <v>43</v>
+        <v>239</v>
+      </c>
+      <c r="F194" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="195" ht="15.15" spans="1:6">
@@ -6524,16 +6764,16 @@
         <v>193</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D195" s="11" t="s">
-        <v>378</v>
+        <v>411</v>
+      </c>
+      <c r="D195" s="12" t="s">
+        <v>412</v>
       </c>
       <c r="E195" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F195" s="13" t="s">
-        <v>43</v>
+        <v>413</v>
+      </c>
+      <c r="F195" s="12" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="196" ht="15.15" spans="1:6">
@@ -6544,16 +6784,16 @@
         <v>194</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D196" s="11" t="s">
-        <v>8</v>
+        <v>415</v>
+      </c>
+      <c r="D196" s="12" t="s">
+        <v>416</v>
       </c>
       <c r="E196" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F196" s="13" t="s">
-        <v>43</v>
+        <v>413</v>
+      </c>
+      <c r="F196" s="12" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="197" ht="15.15" spans="1:6">
@@ -6564,16 +6804,16 @@
         <v>195</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D197" s="11" t="s">
-        <v>8</v>
+        <v>417</v>
+      </c>
+      <c r="D197" s="12" t="s">
+        <v>418</v>
       </c>
       <c r="E197" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F197" s="13" t="s">
-        <v>43</v>
+        <v>413</v>
+      </c>
+      <c r="F197" s="12" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="198" ht="15.15" spans="1:6">
@@ -6584,16 +6824,16 @@
         <v>196</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D198" s="11" t="s">
-        <v>379</v>
+        <v>419</v>
+      </c>
+      <c r="D198" s="12" t="s">
+        <v>420</v>
       </c>
       <c r="E198" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F198" s="13" t="s">
-        <v>43</v>
+        <v>413</v>
+      </c>
+      <c r="F198" s="12" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="199" ht="15.15" spans="1:6">
@@ -6604,16 +6844,16 @@
         <v>197</v>
       </c>
       <c r="C199" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D199" s="11" t="s">
-        <v>380</v>
+        <v>421</v>
+      </c>
+      <c r="D199" s="12" t="s">
+        <v>422</v>
       </c>
       <c r="E199" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F199" s="13" t="s">
-        <v>43</v>
+        <v>413</v>
+      </c>
+      <c r="F199" s="12" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="200" ht="15.15" spans="1:6">
@@ -6624,16 +6864,16 @@
         <v>198</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D200" s="11" t="s">
-        <v>381</v>
+        <v>423</v>
+      </c>
+      <c r="D200" s="12" t="s">
+        <v>424</v>
       </c>
       <c r="E200" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F200" s="13" t="s">
-        <v>43</v>
+        <v>413</v>
+      </c>
+      <c r="F200" s="12" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="201" ht="15.15" spans="1:6">
@@ -6644,16 +6884,16 @@
         <v>199</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D201" s="11" t="s">
-        <v>381</v>
+        <v>425</v>
+      </c>
+      <c r="D201" s="12" t="s">
+        <v>426</v>
       </c>
       <c r="E201" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F201" s="13" t="s">
-        <v>43</v>
+        <v>413</v>
+      </c>
+      <c r="F201" s="12" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="202" ht="15.15" spans="1:6">
@@ -6664,16 +6904,16 @@
         <v>200</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D202" s="11" t="s">
-        <v>382</v>
+        <v>427</v>
+      </c>
+      <c r="D202" s="12" t="s">
+        <v>428</v>
       </c>
       <c r="E202" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F202" s="13" t="s">
-        <v>43</v>
+        <v>413</v>
+      </c>
+      <c r="F202" s="12" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="203" ht="15.15" spans="1:6">
@@ -6684,16 +6924,16 @@
         <v>201</v>
       </c>
       <c r="C203" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D203" s="11" t="s">
-        <v>383</v>
+        <v>429</v>
+      </c>
+      <c r="D203" s="12" t="s">
+        <v>430</v>
       </c>
       <c r="E203" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F203" s="13" t="s">
-        <v>43</v>
+        <v>413</v>
+      </c>
+      <c r="F203" s="12" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="204" ht="15.15" spans="1:6">
@@ -6704,16 +6944,16 @@
         <v>202</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D204" s="11" t="s">
-        <v>384</v>
+        <v>431</v>
+      </c>
+      <c r="D204" s="12" t="s">
+        <v>432</v>
       </c>
       <c r="E204" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F204" s="13" t="s">
-        <v>43</v>
+        <v>413</v>
+      </c>
+      <c r="F204" s="12" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="205" ht="15.15" spans="1:6">
@@ -6724,16 +6964,16 @@
         <v>203</v>
       </c>
       <c r="C205" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D205" s="11" t="s">
-        <v>384</v>
+        <v>433</v>
+      </c>
+      <c r="D205" s="12" t="s">
+        <v>434</v>
       </c>
       <c r="E205" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F205" s="13" t="s">
-        <v>43</v>
+        <v>413</v>
+      </c>
+      <c r="F205" s="12" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="206" ht="15.15" spans="1:6">
@@ -6744,16 +6984,16 @@
         <v>204</v>
       </c>
       <c r="C206" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D206" s="11" t="s">
-        <v>385</v>
+        <v>435</v>
+      </c>
+      <c r="D206" s="12" t="s">
+        <v>436</v>
       </c>
       <c r="E206" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F206" s="13" t="s">
-        <v>43</v>
+        <v>413</v>
+      </c>
+      <c r="F206" s="12" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="207" ht="15.15" spans="1:6">
@@ -6764,16 +7004,16 @@
         <v>205</v>
       </c>
       <c r="C207" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D207" s="11" t="s">
-        <v>386</v>
+        <v>437</v>
+      </c>
+      <c r="D207" s="12" t="s">
+        <v>438</v>
       </c>
       <c r="E207" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F207" s="13" t="s">
-        <v>31</v>
+        <v>439</v>
+      </c>
+      <c r="F207" s="12" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="208" ht="15.15" spans="1:6">
@@ -6784,16 +7024,16 @@
         <v>206</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>387</v>
-      </c>
-      <c r="D208" s="11" t="s">
-        <v>388</v>
+        <v>441</v>
+      </c>
+      <c r="D208" s="12" t="s">
+        <v>442</v>
       </c>
       <c r="E208" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F208" s="13" t="s">
-        <v>31</v>
+        <v>439</v>
+      </c>
+      <c r="F208" s="12" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="209" ht="15.15" spans="1:6">
@@ -6804,16 +7044,16 @@
         <v>207</v>
       </c>
       <c r="C209" s="11" t="s">
-        <v>387</v>
-      </c>
-      <c r="D209" s="11" t="s">
-        <v>389</v>
+        <v>443</v>
+      </c>
+      <c r="D209" s="12" t="s">
+        <v>444</v>
       </c>
       <c r="E209" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F209" s="13" t="s">
-        <v>31</v>
+        <v>439</v>
+      </c>
+      <c r="F209" s="12" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="210" ht="15.15" spans="1:6">
@@ -6824,16 +7064,16 @@
         <v>208</v>
       </c>
       <c r="C210" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="D210" s="11" t="s">
-        <v>391</v>
+        <v>445</v>
+      </c>
+      <c r="D210" s="12" t="s">
+        <v>446</v>
       </c>
       <c r="E210" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F210" s="13" t="s">
-        <v>31</v>
+        <v>439</v>
+      </c>
+      <c r="F210" s="12" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="211" ht="15.15" spans="1:6">
@@ -6844,16 +7084,16 @@
         <v>209</v>
       </c>
       <c r="C211" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="D211" s="11" t="s">
-        <v>392</v>
+        <v>447</v>
+      </c>
+      <c r="D211" s="12" t="s">
+        <v>448</v>
       </c>
       <c r="E211" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F211" s="13" t="s">
-        <v>31</v>
+        <v>439</v>
+      </c>
+      <c r="F211" s="12" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="212" ht="15.15" spans="1:6">
@@ -6864,16 +7104,16 @@
         <v>210</v>
       </c>
       <c r="C212" s="11" t="s">
-        <v>393</v>
-      </c>
-      <c r="D212" s="11" t="s">
-        <v>394</v>
+        <v>449</v>
+      </c>
+      <c r="D212" s="12" t="s">
+        <v>450</v>
       </c>
       <c r="E212" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F212" s="13" t="s">
-        <v>31</v>
+        <v>439</v>
+      </c>
+      <c r="F212" s="12" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="213" ht="15.15" spans="1:6">
@@ -6884,16 +7124,16 @@
         <v>211</v>
       </c>
       <c r="C213" s="11" t="s">
-        <v>393</v>
-      </c>
-      <c r="D213" s="11" t="s">
-        <v>395</v>
+        <v>451</v>
+      </c>
+      <c r="D213" s="12" t="s">
+        <v>452</v>
       </c>
       <c r="E213" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F213" s="13" t="s">
-        <v>31</v>
+        <v>439</v>
+      </c>
+      <c r="F213" s="12" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="214" ht="15.15" spans="1:6">
@@ -6904,16 +7144,16 @@
         <v>212</v>
       </c>
       <c r="C214" s="11" t="s">
-        <v>393</v>
-      </c>
-      <c r="D214" s="11" t="s">
-        <v>396</v>
+        <v>453</v>
+      </c>
+      <c r="D214" s="12" t="s">
+        <v>454</v>
       </c>
       <c r="E214" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F214" s="13" t="s">
-        <v>31</v>
+        <v>439</v>
+      </c>
+      <c r="F214" s="12" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="215" ht="15.15" spans="1:6">
@@ -6924,16 +7164,16 @@
         <v>213</v>
       </c>
       <c r="C215" s="11" t="s">
-        <v>397</v>
-      </c>
-      <c r="D215" s="11" t="s">
-        <v>12</v>
+        <v>455</v>
+      </c>
+      <c r="D215" s="12" t="s">
+        <v>456</v>
       </c>
       <c r="E215" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F215" s="13" t="s">
-        <v>31</v>
+        <v>439</v>
+      </c>
+      <c r="F215" s="12" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="216" ht="15.15" spans="1:6">
@@ -6944,16 +7184,16 @@
         <v>214</v>
       </c>
       <c r="C216" s="11" t="s">
-        <v>397</v>
-      </c>
-      <c r="D216" s="11" t="s">
-        <v>398</v>
+        <v>457</v>
+      </c>
+      <c r="D216" s="12" t="s">
+        <v>458</v>
       </c>
       <c r="E216" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F216" s="13" t="s">
-        <v>31</v>
+        <v>439</v>
+      </c>
+      <c r="F216" s="12" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="217" ht="15.15" spans="1:6">
@@ -6964,16 +7204,16 @@
         <v>215</v>
       </c>
       <c r="C217" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="D217" s="11" t="s">
-        <v>400</v>
+        <v>459</v>
+      </c>
+      <c r="D217" s="12" t="s">
+        <v>460</v>
       </c>
       <c r="E217" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F217" s="13" t="s">
-        <v>31</v>
+        <v>439</v>
+      </c>
+      <c r="F217" s="12" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="218" ht="15.15" spans="1:6">
@@ -6984,16 +7224,16 @@
         <v>216</v>
       </c>
       <c r="C218" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="D218" s="11" t="s">
-        <v>401</v>
+        <v>461</v>
+      </c>
+      <c r="D218" s="12" t="s">
+        <v>462</v>
       </c>
       <c r="E218" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F218" s="13" t="s">
-        <v>31</v>
+        <v>439</v>
+      </c>
+      <c r="F218" s="12" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="219" ht="15.15" spans="1:6">
@@ -7004,16 +7244,16 @@
         <v>217</v>
       </c>
       <c r="C219" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="D219" s="11" t="s">
-        <v>401</v>
+        <v>463</v>
+      </c>
+      <c r="D219" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="E219" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F219" s="13" t="s">
-        <v>89</v>
+        <v>465</v>
+      </c>
+      <c r="F219" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="220" ht="15.15" spans="1:6">
@@ -7024,16 +7264,16 @@
         <v>218</v>
       </c>
       <c r="C220" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="D220" s="11" t="s">
-        <v>402</v>
+        <v>466</v>
+      </c>
+      <c r="D220" s="12" t="s">
+        <v>467</v>
       </c>
       <c r="E220" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F220" s="13" t="s">
-        <v>89</v>
+        <v>465</v>
+      </c>
+      <c r="F220" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="221" ht="15.15" spans="1:6">
@@ -7044,16 +7284,16 @@
         <v>219</v>
       </c>
       <c r="C221" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="D221" s="11" t="s">
-        <v>402</v>
+        <v>468</v>
+      </c>
+      <c r="D221" s="12" t="s">
+        <v>469</v>
       </c>
       <c r="E221" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F221" s="13" t="s">
-        <v>89</v>
+        <v>465</v>
+      </c>
+      <c r="F221" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="222" ht="15.15" spans="1:6">
@@ -7064,16 +7304,16 @@
         <v>220</v>
       </c>
       <c r="C222" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="D222" s="11" t="s">
-        <v>402</v>
+        <v>470</v>
+      </c>
+      <c r="D222" s="12" t="s">
+        <v>471</v>
       </c>
       <c r="E222" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F222" s="13" t="s">
-        <v>89</v>
+        <v>465</v>
+      </c>
+      <c r="F222" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="223" ht="15.15" spans="1:6">
@@ -7084,16 +7324,16 @@
         <v>221</v>
       </c>
       <c r="C223" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="D223" s="11" t="s">
-        <v>403</v>
+        <v>472</v>
+      </c>
+      <c r="D223" s="12" t="s">
+        <v>473</v>
       </c>
       <c r="E223" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F223" s="13" t="s">
-        <v>89</v>
+        <v>465</v>
+      </c>
+      <c r="F223" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="224" ht="15.15" spans="1:6">
@@ -7104,16 +7344,16 @@
         <v>222</v>
       </c>
       <c r="C224" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="D224" s="11" t="s">
-        <v>403</v>
+        <v>474</v>
+      </c>
+      <c r="D224" s="12" t="s">
+        <v>475</v>
       </c>
       <c r="E224" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F224" s="13" t="s">
-        <v>89</v>
+        <v>465</v>
+      </c>
+      <c r="F224" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="225" ht="15.15" spans="1:6">
@@ -7124,16 +7364,16 @@
         <v>223</v>
       </c>
       <c r="C225" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="D225" s="11" t="s">
-        <v>403</v>
+        <v>476</v>
+      </c>
+      <c r="D225" s="12" t="s">
+        <v>477</v>
       </c>
       <c r="E225" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F225" s="13" t="s">
-        <v>89</v>
+        <v>465</v>
+      </c>
+      <c r="F225" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="226" ht="15.15" spans="1:6">
@@ -7144,16 +7384,16 @@
         <v>224</v>
       </c>
       <c r="C226" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="D226" s="11" t="s">
-        <v>404</v>
+        <v>478</v>
+      </c>
+      <c r="D226" s="12" t="s">
+        <v>479</v>
       </c>
       <c r="E226" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F226" s="13" t="s">
-        <v>89</v>
+        <v>465</v>
+      </c>
+      <c r="F226" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="227" ht="15.15" spans="1:6">
@@ -7164,16 +7404,16 @@
         <v>225</v>
       </c>
       <c r="C227" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="D227" s="11" t="s">
-        <v>404</v>
+        <v>480</v>
+      </c>
+      <c r="D227" s="12" t="s">
+        <v>481</v>
       </c>
       <c r="E227" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F227" s="13" t="s">
-        <v>89</v>
+        <v>465</v>
+      </c>
+      <c r="F227" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="228" ht="15.15" spans="1:6">
@@ -7184,16 +7424,16 @@
         <v>226</v>
       </c>
       <c r="C228" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="D228" s="11" t="s">
-        <v>404</v>
+        <v>482</v>
+      </c>
+      <c r="D228" s="12" t="s">
+        <v>483</v>
       </c>
       <c r="E228" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F228" s="13" t="s">
-        <v>89</v>
+        <v>465</v>
+      </c>
+      <c r="F228" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="229" ht="15.15" spans="1:6">
@@ -7204,36 +7444,36 @@
         <v>227</v>
       </c>
       <c r="C229" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="D229" s="11" t="s">
-        <v>405</v>
+        <v>484</v>
+      </c>
+      <c r="D229" s="12" t="s">
+        <v>485</v>
       </c>
       <c r="E229" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F229" s="13" t="s">
-        <v>89</v>
+        <v>465</v>
+      </c>
+      <c r="F229" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="230" ht="15.15" spans="1:6">
-      <c r="A230" s="14">
+      <c r="A230" s="13">
         <v>19</v>
       </c>
-      <c r="B230" s="15">
+      <c r="B230" s="14">
         <v>228</v>
       </c>
-      <c r="C230" s="16" t="s">
-        <v>399</v>
+      <c r="C230" s="15" t="s">
+        <v>486</v>
       </c>
       <c r="D230" s="16" t="s">
-        <v>405</v>
-      </c>
-      <c r="E230" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="F230" s="18" t="s">
-        <v>89</v>
+        <v>487</v>
+      </c>
+      <c r="E230" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="F230" s="16" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
